--- a/rocps-automation/src/main/resources/SystemTestCases.xlsx
+++ b/rocps-automation/src/main/resources/SystemTestCases.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ROCPS_Automation\ROCPS_Automation\rocps-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aditya.verma\rocps_web_automation_master\rocps_web_automation\rocps-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65A6A14C-7F47-4642-B760-1190B765DD7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E33A3165-C830-4F42-ADF9-63309E711E82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" firstSheet="17" activeTab="21" xr2:uid="{D8B6B6A8-A5A3-42FE-B72B-662B784A80DE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D8B6B6A8-A5A3-42FE-B72B-662B784A80DE}"/>
   </bookViews>
   <sheets>
     <sheet name="Pre-requisites" sheetId="1" r:id="rId1"/>
@@ -4150,9 +4150,6 @@
     <t>DataDir;Birt;</t>
   </si>
   <si>
-    <t>$$machineName|7770|7777</t>
-  </si>
-  <si>
     <t>Billing Stream</t>
   </si>
   <si>
@@ -4188,9 +4185,6 @@
   </si>
   <si>
     <t>Machine *|Max Weightage *|Static Max Weightage *|Controller Listen Port *</t>
-  </si>
-  <si>
-    <t>$$machineName|20|20|7779</t>
   </si>
   <si>
     <t>0|13</t>
@@ -4768,6 +4762,12 @@
   </si>
   <si>
     <t>2,34.8000;USD;Accepted;01/01/2025;01/31/2025</t>
+  </si>
+  <si>
+    <t>$$machineName|20|20|7788</t>
+  </si>
+  <si>
+    <t>$$machineName|7771|7789</t>
   </si>
 </sst>
 </file>
@@ -4944,7 +4944,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -5059,9 +5059,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -5644,7 +5641,7 @@
         <v>153</v>
       </c>
       <c r="AD3" s="7" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="4" spans="1:30" ht="105" x14ac:dyDescent="0.25">
@@ -5702,7 +5699,7 @@
         <v>44</v>
       </c>
       <c r="AA4" s="4" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="5" spans="1:30" ht="45" x14ac:dyDescent="0.25">
@@ -5749,14 +5746,14 @@
         <v>46</v>
       </c>
       <c r="X5" s="4" t="s">
-        <v>1364</v>
+        <v>1561</v>
       </c>
       <c r="Y5" s="4"/>
       <c r="Z5" s="4" t="s">
         <v>46</v>
       </c>
       <c r="AA5" s="4" t="s">
-        <v>1377</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="6" spans="1:30" ht="30" x14ac:dyDescent="0.25">
@@ -5842,10 +5839,10 @@
         <v>25</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="Q8" s="4"/>
       <c r="R8" s="4"/>
@@ -5874,10 +5871,10 @@
         <v>26</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="Q9" s="4"/>
       <c r="R9" s="4"/>
@@ -5906,10 +5903,10 @@
         <v>27</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
       <c r="Q10" s="4"/>
       <c r="R10" s="4"/>
@@ -5938,10 +5935,10 @@
         <v>28</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="Q11" s="4"/>
       <c r="R11" s="4"/>
@@ -6235,7 +6232,7 @@
       </c>
       <c r="L21" s="4"/>
       <c r="M21" s="4" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="Q21" s="4"/>
       <c r="R21" s="4"/>
@@ -7106,7 +7103,7 @@
       </c>
       <c r="BA3" s="7"/>
       <c r="BB3" s="7" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
       <c r="BC3" s="7" t="s">
         <v>874</v>
@@ -7275,7 +7272,7 @@
       </c>
       <c r="BG4" s="4"/>
       <c r="BH4" s="4" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="BI4" s="4" t="s">
         <v>568</v>
@@ -7408,10 +7405,10 @@
       <c r="AZ5" s="7"/>
       <c r="BA5" s="7"/>
       <c r="BB5" s="26" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
       <c r="BC5" s="25" t="s">
-        <v>1490</v>
+        <v>1488</v>
       </c>
       <c r="BD5" s="18"/>
       <c r="BE5" s="4" t="s">
@@ -7422,7 +7419,7 @@
       </c>
       <c r="BG5" s="4"/>
       <c r="BH5" s="4" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="BI5" s="4"/>
       <c r="BJ5" s="18"/>
@@ -7450,7 +7447,7 @@
         <v>173</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
       <c r="H6" s="7"/>
       <c r="I6" s="7" t="s">
@@ -7517,7 +7514,7 @@
       <c r="AN6" s="7"/>
       <c r="AO6" s="7"/>
       <c r="AP6" s="7" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="AQ6" s="7"/>
       <c r="AR6" s="7"/>
@@ -7654,7 +7651,7 @@
       <c r="AN7" s="7"/>
       <c r="AO7" s="7"/>
       <c r="AP7" s="7" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="AQ7" s="7"/>
       <c r="AR7" s="7"/>
@@ -7779,7 +7776,7 @@
       <c r="AN8" s="7"/>
       <c r="AO8" s="7"/>
       <c r="AP8" s="7" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="AQ8" s="7"/>
       <c r="AR8" s="7"/>
@@ -7806,20 +7803,20 @@
       <c r="BC8" s="7"/>
       <c r="BD8" s="18"/>
       <c r="BE8" s="18" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="BF8" s="18" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="BG8" s="4"/>
       <c r="BH8" s="7"/>
       <c r="BI8" s="7"/>
       <c r="BJ8" s="18"/>
       <c r="BK8" s="18" t="s">
+        <v>1419</v>
+      </c>
+      <c r="BL8" s="18" t="s">
         <v>1421</v>
-      </c>
-      <c r="BL8" s="18" t="s">
-        <v>1423</v>
       </c>
       <c r="BM8" s="7"/>
       <c r="BN8" s="7" t="s">
@@ -7896,7 +7893,7 @@
       <c r="AN9" s="7"/>
       <c r="AO9" s="7"/>
       <c r="AP9" s="7" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="AQ9" s="7"/>
       <c r="AR9" s="7"/>
@@ -8013,7 +8010,7 @@
       <c r="AN10" s="7"/>
       <c r="AO10" s="7"/>
       <c r="AP10" s="7" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="AQ10" s="7"/>
       <c r="AR10" s="7"/>
@@ -8118,7 +8115,7 @@
       <c r="AN11" s="7"/>
       <c r="AO11" s="7"/>
       <c r="AP11" s="7" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="AQ11" s="7"/>
       <c r="AR11" s="7"/>
@@ -8169,7 +8166,7 @@
         <v>252</v>
       </c>
       <c r="J12" s="26" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4" t="s">
@@ -8616,7 +8613,7 @@
         <v>257</v>
       </c>
       <c r="J17" s="26" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="K17" s="7"/>
       <c r="L17" s="7"/>
@@ -8685,7 +8682,7 @@
         <v>475</v>
       </c>
       <c r="BO17" s="25" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="18" spans="1:67" ht="105" x14ac:dyDescent="0.25">
@@ -8774,7 +8771,7 @@
         <v>476</v>
       </c>
       <c r="BO18" s="25" t="s">
-        <v>1456</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="19" spans="1:67" ht="105" x14ac:dyDescent="0.25">
@@ -8863,7 +8860,7 @@
         <v>845</v>
       </c>
       <c r="BO19" s="25" t="s">
-        <v>1457</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="20" spans="1:67" ht="105" x14ac:dyDescent="0.25">
@@ -8956,7 +8953,7 @@
         <v>916</v>
       </c>
       <c r="BO20" s="7" t="s">
-        <v>1458</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="21" spans="1:67" ht="30" x14ac:dyDescent="0.25">
@@ -9243,7 +9240,7 @@
         <v>329</v>
       </c>
       <c r="AB24" s="4" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="AC24" s="4"/>
       <c r="AD24" s="4"/>
@@ -10212,7 +10209,7 @@
       <c r="AW36" s="7"/>
       <c r="AX36" s="7"/>
       <c r="AY36" s="7" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
       <c r="AZ36" s="7"/>
       <c r="BA36" s="7"/>
@@ -10291,7 +10288,7 @@
       <c r="AW37" s="7"/>
       <c r="AX37" s="7"/>
       <c r="AY37" s="7" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="AZ37" s="7"/>
       <c r="BA37" s="7"/>
@@ -10685,45 +10682,45 @@
     </row>
     <row r="43" spans="1:67" x14ac:dyDescent="0.25">
       <c r="F43" s="7" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="44" spans="1:67" x14ac:dyDescent="0.25">
       <c r="F44" s="7" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="G44" s="7"/>
     </row>
     <row r="45" spans="1:67" x14ac:dyDescent="0.25">
       <c r="F45" s="7" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="G45" s="7"/>
     </row>
     <row r="46" spans="1:67" x14ac:dyDescent="0.25">
       <c r="F46" s="7" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="G46" s="7"/>
     </row>
     <row r="47" spans="1:67" x14ac:dyDescent="0.25">
       <c r="F47" s="7" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="G47" s="7"/>
     </row>
     <row r="48" spans="1:67" x14ac:dyDescent="0.25">
       <c r="F48" s="7" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="G48" s="7"/>
     </row>
     <row r="49" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F49" s="7" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="G49" s="7"/>
     </row>
@@ -11235,7 +11232,7 @@
       </c>
       <c r="AU3" s="7"/>
       <c r="AV3" s="7" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
       <c r="AW3" s="7" t="s">
         <v>1054</v>
@@ -11397,7 +11394,7 @@
       </c>
       <c r="BA4" s="4"/>
       <c r="BB4" s="4" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="BC4" s="4" t="s">
         <v>568</v>
@@ -11523,10 +11520,10 @@
       <c r="AT5" s="7"/>
       <c r="AU5" s="7"/>
       <c r="AV5" s="26" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
       <c r="AW5" s="25" t="s">
-        <v>1490</v>
+        <v>1488</v>
       </c>
       <c r="AX5" s="18"/>
       <c r="AY5" s="4" t="s">
@@ -11537,7 +11534,7 @@
       </c>
       <c r="BA5" s="4"/>
       <c r="BB5" s="4" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="BC5" s="4"/>
       <c r="BD5" s="18"/>
@@ -11564,7 +11561,7 @@
         <v>173</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
       <c r="D6" s="7"/>
       <c r="E6" s="7" t="s">
@@ -11623,7 +11620,7 @@
       <c r="AH6" s="7"/>
       <c r="AI6" s="7"/>
       <c r="AJ6" s="7" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="AK6" s="7"/>
       <c r="AL6" s="7"/>
@@ -11751,7 +11748,7 @@
       <c r="AH7" s="7"/>
       <c r="AI7" s="7"/>
       <c r="AJ7" s="7" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="AK7" s="7"/>
       <c r="AL7" s="7"/>
@@ -11871,7 +11868,7 @@
       <c r="AH8" s="7"/>
       <c r="AI8" s="7"/>
       <c r="AJ8" s="7" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="AK8" s="7"/>
       <c r="AL8" s="7"/>
@@ -11898,20 +11895,20 @@
       <c r="AW8" s="7"/>
       <c r="AX8" s="18"/>
       <c r="AY8" s="18" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="AZ8" s="18" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="BA8" s="4"/>
       <c r="BB8" s="7"/>
       <c r="BC8" s="7"/>
       <c r="BD8" s="18"/>
       <c r="BE8" s="18" t="s">
+        <v>1419</v>
+      </c>
+      <c r="BF8" s="18" t="s">
         <v>1421</v>
-      </c>
-      <c r="BF8" s="18" t="s">
-        <v>1423</v>
       </c>
       <c r="BG8" s="7"/>
       <c r="BH8" s="7" t="s">
@@ -11981,7 +11978,7 @@
       <c r="AH9" s="7"/>
       <c r="AI9" s="7"/>
       <c r="AJ9" s="7" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="AK9" s="7"/>
       <c r="AL9" s="7"/>
@@ -12087,7 +12084,7 @@
       <c r="AH10" s="7"/>
       <c r="AI10" s="7"/>
       <c r="AJ10" s="7" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="AK10" s="7"/>
       <c r="AL10" s="7"/>
@@ -12181,7 +12178,7 @@
       <c r="AH11" s="7"/>
       <c r="AI11" s="7"/>
       <c r="AJ11" s="7" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="AK11" s="7"/>
       <c r="AL11" s="7"/>
@@ -12229,10 +12226,10 @@
         <v>252</v>
       </c>
       <c r="F12" s="26" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="G12" s="26" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="H12" s="4"/>
       <c r="I12" s="4" t="s">
@@ -12655,10 +12652,10 @@
         <v>257</v>
       </c>
       <c r="F17" s="26" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="G17" s="26" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="H17" s="7"/>
       <c r="I17" s="7"/>
@@ -12724,10 +12721,10 @@
         <v>475</v>
       </c>
       <c r="BI17" s="25" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
       <c r="BJ17" s="25" t="s">
-        <v>1442</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="18" spans="1:62" ht="123.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12812,10 +12809,10 @@
         <v>476</v>
       </c>
       <c r="BI18" s="25" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
       <c r="BJ18" s="25" t="s">
-        <v>1443</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="19" spans="1:62" ht="120" x14ac:dyDescent="0.25">
@@ -12900,10 +12897,10 @@
         <v>845</v>
       </c>
       <c r="BI19" s="25" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="BJ19" s="25" t="s">
-        <v>1444</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="20" spans="1:62" ht="45" x14ac:dyDescent="0.25">
@@ -13263,7 +13260,7 @@
         <v>329</v>
       </c>
       <c r="V24" s="4" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="W24" s="4"/>
       <c r="X24" s="4"/>
@@ -14194,7 +14191,7 @@
       <c r="AQ36" s="7"/>
       <c r="AR36" s="7"/>
       <c r="AS36" s="7" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
       <c r="AT36" s="7"/>
       <c r="AU36" s="7"/>
@@ -14270,7 +14267,7 @@
       <c r="AQ37" s="7"/>
       <c r="AR37" s="7"/>
       <c r="AS37" s="7" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="AT37" s="7"/>
       <c r="AU37" s="7"/>
@@ -14647,10 +14644,10 @@
     <row r="43" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A43" s="18"/>
       <c r="B43" s="7" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="D43" s="18"/>
       <c r="E43" s="18"/>
@@ -14715,7 +14712,7 @@
     <row r="44" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A44" s="18"/>
       <c r="B44" s="7" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="C44" s="7"/>
       <c r="D44" s="18"/>
@@ -14781,7 +14778,7 @@
     <row r="45" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A45" s="18"/>
       <c r="B45" s="7" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="C45" s="7"/>
       <c r="D45" s="18"/>
@@ -14847,7 +14844,7 @@
     <row r="46" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A46" s="18"/>
       <c r="B46" s="7" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="C46" s="7"/>
       <c r="D46" s="18"/>
@@ -14913,7 +14910,7 @@
     <row r="47" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A47" s="18"/>
       <c r="B47" s="7" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="C47" s="7"/>
       <c r="D47" s="18"/>
@@ -14979,7 +14976,7 @@
     <row r="48" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A48" s="18"/>
       <c r="B48" s="7" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="C48" s="7"/>
       <c r="D48" s="18"/>
@@ -15045,7 +15042,7 @@
     <row r="49" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A49" s="18"/>
       <c r="B49" s="7" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="C49" s="7"/>
       <c r="D49" s="18"/>
@@ -15694,7 +15691,7 @@
       </c>
       <c r="BD3" s="7"/>
       <c r="BE3" s="7" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
       <c r="BF3" s="7" t="s">
         <v>1055</v>
@@ -15881,7 +15878,7 @@
       </c>
       <c r="BJ4" s="4"/>
       <c r="BK4" s="4" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="BL4" s="4" t="s">
         <v>568</v>
@@ -16030,10 +16027,10 @@
       <c r="BC5" s="7"/>
       <c r="BD5" s="7"/>
       <c r="BE5" s="26" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
       <c r="BF5" s="25" t="s">
-        <v>1490</v>
+        <v>1488</v>
       </c>
       <c r="BG5" s="7"/>
       <c r="BH5" s="4" t="s">
@@ -16044,7 +16041,7 @@
       </c>
       <c r="BJ5" s="4"/>
       <c r="BK5" s="4" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="BL5" s="4"/>
       <c r="BM5" s="7"/>
@@ -16071,10 +16068,10 @@
         <v>173</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
       <c r="E6" s="7"/>
       <c r="F6" s="7" t="s">
@@ -16145,7 +16142,7 @@
       <c r="AO6" s="7"/>
       <c r="AP6" s="7"/>
       <c r="AQ6" s="7" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="AR6" s="7"/>
       <c r="AS6" s="7"/>
@@ -16292,7 +16289,7 @@
       <c r="AO7" s="7"/>
       <c r="AP7" s="7"/>
       <c r="AQ7" s="7" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="AR7" s="7"/>
       <c r="AS7" s="7"/>
@@ -16429,7 +16426,7 @@
       <c r="AO8" s="7"/>
       <c r="AP8" s="7"/>
       <c r="AQ8" s="7" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="AR8" s="7"/>
       <c r="AS8" s="7"/>
@@ -16460,20 +16457,20 @@
       <c r="BF8" s="7"/>
       <c r="BG8" s="7"/>
       <c r="BH8" s="18" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="BI8" s="18" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="BJ8" s="4"/>
       <c r="BK8" s="7"/>
       <c r="BL8" s="7"/>
       <c r="BM8" s="7"/>
       <c r="BN8" s="18" t="s">
+        <v>1419</v>
+      </c>
+      <c r="BO8" s="18" t="s">
         <v>1421</v>
-      </c>
-      <c r="BO8" s="18" t="s">
-        <v>1423</v>
       </c>
       <c r="BP8" s="7"/>
       <c r="BQ8" s="7" t="s">
@@ -16556,7 +16553,7 @@
       <c r="AO9" s="7"/>
       <c r="AP9" s="7"/>
       <c r="AQ9" s="7" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="AR9" s="7"/>
       <c r="AS9" s="7"/>
@@ -16684,7 +16681,7 @@
       <c r="AO10" s="7"/>
       <c r="AP10" s="7"/>
       <c r="AQ10" s="7" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="AR10" s="7"/>
       <c r="AS10" s="7"/>
@@ -16797,7 +16794,7 @@
       <c r="AO11" s="7"/>
       <c r="AP11" s="7"/>
       <c r="AQ11" s="7" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="AR11" s="7"/>
       <c r="AS11" s="7"/>
@@ -16848,10 +16845,10 @@
         <v>252</v>
       </c>
       <c r="G12" s="26" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="H12" s="26" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="I12" s="4"/>
       <c r="J12" s="4" t="s">
@@ -17333,10 +17330,10 @@
         <v>257</v>
       </c>
       <c r="G17" s="26" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="H17" s="26" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
@@ -17412,10 +17409,10 @@
         <v>475</v>
       </c>
       <c r="BR17" s="25" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
       <c r="BS17" s="25" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="18" spans="1:71" ht="90" x14ac:dyDescent="0.25">
@@ -17513,10 +17510,10 @@
         <v>476</v>
       </c>
       <c r="BR18" s="25" t="s">
-        <v>1448</v>
+        <v>1446</v>
       </c>
       <c r="BS18" s="25" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="19" spans="1:71" ht="90" x14ac:dyDescent="0.25">
@@ -17614,10 +17611,10 @@
         <v>845</v>
       </c>
       <c r="BR19" s="25" t="s">
-        <v>1449</v>
+        <v>1447</v>
       </c>
       <c r="BS19" s="25" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="20" spans="1:71" ht="90" x14ac:dyDescent="0.25">
@@ -17721,10 +17718,10 @@
         <v>916</v>
       </c>
       <c r="BR20" s="25" t="s">
-        <v>1450</v>
+        <v>1448</v>
       </c>
       <c r="BS20" s="25" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="21" spans="1:71" x14ac:dyDescent="0.25">
@@ -18033,10 +18030,10 @@
         <v>329</v>
       </c>
       <c r="X24" s="4" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="Y24" s="4" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="Z24" s="4"/>
       <c r="AA24" s="4"/>
@@ -19093,7 +19090,7 @@
       <c r="AZ36" s="7"/>
       <c r="BA36" s="7"/>
       <c r="BB36" s="7" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
       <c r="BC36" s="7"/>
       <c r="BD36" s="7"/>
@@ -19180,7 +19177,7 @@
       <c r="AZ37" s="7"/>
       <c r="BA37" s="7"/>
       <c r="BB37" s="7" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="BC37" s="7"/>
       <c r="BD37" s="7"/>
@@ -19603,53 +19600,53 @@
     </row>
     <row r="43" spans="1:71" x14ac:dyDescent="0.25">
       <c r="B43" s="7" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="44" spans="1:71" x14ac:dyDescent="0.25">
       <c r="B44" s="7" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="C44" s="7"/>
       <c r="D44" s="7"/>
     </row>
     <row r="45" spans="1:71" x14ac:dyDescent="0.25">
       <c r="B45" s="7" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="C45" s="7"/>
       <c r="D45" s="7"/>
     </row>
     <row r="46" spans="1:71" x14ac:dyDescent="0.25">
       <c r="B46" s="7" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="C46" s="7"/>
       <c r="D46" s="7"/>
     </row>
     <row r="47" spans="1:71" x14ac:dyDescent="0.25">
       <c r="B47" s="7" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="C47" s="7"/>
       <c r="D47" s="7"/>
     </row>
     <row r="48" spans="1:71" x14ac:dyDescent="0.25">
       <c r="B48" s="7" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="C48" s="7"/>
       <c r="D48" s="7"/>
     </row>
     <row r="49" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B49" s="7" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="C49" s="7"/>
       <c r="D49" s="7"/>
@@ -20158,7 +20155,7 @@
       </c>
       <c r="AU3" s="7"/>
       <c r="AV3" s="7" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
       <c r="AW3" s="7" t="s">
         <v>912</v>
@@ -20319,7 +20316,7 @@
       </c>
       <c r="BA4" s="4"/>
       <c r="BB4" s="4" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="BC4" s="4" t="s">
         <v>568</v>
@@ -20444,10 +20441,10 @@
       <c r="AT5" s="7"/>
       <c r="AU5" s="7"/>
       <c r="AV5" s="26" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
       <c r="AW5" s="25" t="s">
-        <v>1490</v>
+        <v>1488</v>
       </c>
       <c r="AX5" s="18"/>
       <c r="AY5" s="4" t="s">
@@ -20458,7 +20455,7 @@
       </c>
       <c r="BA5" s="4"/>
       <c r="BB5" s="4" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="BC5" s="4"/>
       <c r="BD5" s="18"/>
@@ -20484,7 +20481,7 @@
         <v>173</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
       <c r="D6" s="7"/>
       <c r="E6" s="7" t="s">
@@ -20545,7 +20542,7 @@
       <c r="AH6" s="7"/>
       <c r="AI6" s="7"/>
       <c r="AJ6" s="7" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="AK6" s="7"/>
       <c r="AL6" s="7"/>
@@ -20674,7 +20671,7 @@
       <c r="AH7" s="7"/>
       <c r="AI7" s="7"/>
       <c r="AJ7" s="7" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="AK7" s="7"/>
       <c r="AL7" s="7"/>
@@ -20795,7 +20792,7 @@
       <c r="AH8" s="7"/>
       <c r="AI8" s="7"/>
       <c r="AJ8" s="7" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="AK8" s="7"/>
       <c r="AL8" s="7"/>
@@ -20822,20 +20819,20 @@
       <c r="AW8" s="7"/>
       <c r="AX8" s="18"/>
       <c r="AY8" s="18" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="AZ8" s="18" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="BA8" s="4"/>
       <c r="BB8" s="7"/>
       <c r="BC8" s="7"/>
       <c r="BD8" s="18"/>
       <c r="BE8" s="18" t="s">
+        <v>1419</v>
+      </c>
+      <c r="BF8" s="18" t="s">
         <v>1421</v>
-      </c>
-      <c r="BF8" s="18" t="s">
-        <v>1423</v>
       </c>
       <c r="BG8" s="7"/>
       <c r="BH8" s="7" t="s">
@@ -20906,7 +20903,7 @@
       <c r="AH9" s="7"/>
       <c r="AI9" s="7"/>
       <c r="AJ9" s="7" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="AK9" s="7"/>
       <c r="AL9" s="7"/>
@@ -21015,7 +21012,7 @@
       <c r="AH10" s="7"/>
       <c r="AI10" s="7"/>
       <c r="AJ10" s="7" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="AK10" s="7"/>
       <c r="AL10" s="7"/>
@@ -21112,7 +21109,7 @@
       <c r="AH11" s="7"/>
       <c r="AI11" s="7"/>
       <c r="AJ11" s="7" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="AK11" s="7"/>
       <c r="AL11" s="7"/>
@@ -21161,7 +21158,7 @@
         <v>252</v>
       </c>
       <c r="F12" s="26" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="G12" s="4"/>
       <c r="H12" s="4" t="s">
@@ -21586,7 +21583,7 @@
         <v>257</v>
       </c>
       <c r="F17" s="26" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="G17" s="7"/>
       <c r="H17" s="7"/>
@@ -21653,7 +21650,7 @@
         <v>475</v>
       </c>
       <c r="BI17" s="25" t="s">
-        <v>1491</v>
+        <v>1489</v>
       </c>
       <c r="BK17" s="7"/>
       <c r="BL17" s="25"/>
@@ -21738,7 +21735,7 @@
         <v>476</v>
       </c>
       <c r="BI18" s="25" t="s">
-        <v>1492</v>
+        <v>1490</v>
       </c>
       <c r="BK18" s="7"/>
       <c r="BL18" s="25"/>
@@ -21823,7 +21820,7 @@
         <v>845</v>
       </c>
       <c r="BI19" s="25" t="s">
-        <v>1493</v>
+        <v>1491</v>
       </c>
       <c r="BK19" s="7"/>
       <c r="BL19" s="25"/>
@@ -22173,7 +22170,7 @@
         <v>329</v>
       </c>
       <c r="V24" s="4" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="W24" s="4"/>
       <c r="X24" s="4"/>
@@ -23070,7 +23067,7 @@
       <c r="AQ36" s="7"/>
       <c r="AR36" s="7"/>
       <c r="AS36" s="7" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
       <c r="AT36" s="7"/>
       <c r="AU36" s="7"/>
@@ -23143,7 +23140,7 @@
       <c r="AQ37" s="7"/>
       <c r="AR37" s="7"/>
       <c r="AS37" s="7" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="AT37" s="7"/>
       <c r="AU37" s="7"/>
@@ -23507,45 +23504,45 @@
     </row>
     <row r="43" spans="1:61" x14ac:dyDescent="0.25">
       <c r="B43" s="7" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="44" spans="1:61" x14ac:dyDescent="0.25">
       <c r="B44" s="7" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="C44" s="7"/>
     </row>
     <row r="45" spans="1:61" x14ac:dyDescent="0.25">
       <c r="B45" s="7" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="C45" s="7"/>
     </row>
     <row r="46" spans="1:61" x14ac:dyDescent="0.25">
       <c r="B46" s="7" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="C46" s="7"/>
     </row>
     <row r="47" spans="1:61" x14ac:dyDescent="0.25">
       <c r="B47" s="7" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="C47" s="7"/>
     </row>
     <row r="48" spans="1:61" x14ac:dyDescent="0.25">
       <c r="B48" s="7" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="C48" s="7"/>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B49" s="7" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="C49" s="7"/>
     </row>
@@ -24047,7 +24044,7 @@
       </c>
       <c r="AU3" s="7"/>
       <c r="AV3" s="7" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
       <c r="AW3" s="7" t="s">
         <v>929</v>
@@ -24202,7 +24199,7 @@
       </c>
       <c r="BA4" s="4"/>
       <c r="BB4" s="4" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="BC4" s="4" t="s">
         <v>568</v>
@@ -24322,10 +24319,10 @@
       <c r="AT5" s="7"/>
       <c r="AU5" s="7"/>
       <c r="AV5" s="26" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
       <c r="AW5" s="25" t="s">
-        <v>1490</v>
+        <v>1488</v>
       </c>
       <c r="AX5" s="18"/>
       <c r="AY5" s="4" t="s">
@@ -24336,7 +24333,7 @@
       </c>
       <c r="BA5" s="4"/>
       <c r="BB5" s="4" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="BC5" s="4"/>
       <c r="BD5" s="18"/>
@@ -24360,7 +24357,7 @@
         <v>173</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
       <c r="D6" s="7"/>
       <c r="E6" s="7" t="s">
@@ -24414,7 +24411,7 @@
       <c r="AG6" s="7"/>
       <c r="AH6" s="7"/>
       <c r="AI6" s="7" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="AJ6" s="7"/>
       <c r="AK6" s="7"/>
@@ -24541,7 +24538,7 @@
       <c r="AG7" s="7"/>
       <c r="AH7" s="7"/>
       <c r="AI7" s="7" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="AJ7" s="7"/>
       <c r="AK7" s="7"/>
@@ -24659,7 +24656,7 @@
       <c r="AG8" s="7"/>
       <c r="AH8" s="7"/>
       <c r="AI8" s="7" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="AJ8" s="7"/>
       <c r="AK8" s="7"/>
@@ -24689,20 +24686,20 @@
       <c r="AW8" s="7"/>
       <c r="AX8" s="18"/>
       <c r="AY8" s="18" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="AZ8" s="18" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="BA8" s="4"/>
       <c r="BB8" s="7"/>
       <c r="BC8" s="7"/>
       <c r="BD8" s="18"/>
       <c r="BE8" s="18" t="s">
+        <v>1419</v>
+      </c>
+      <c r="BF8" s="18" t="s">
         <v>1421</v>
-      </c>
-      <c r="BF8" s="18" t="s">
-        <v>1423</v>
       </c>
       <c r="BG8" s="7"/>
       <c r="BH8" s="7" t="s">
@@ -24767,7 +24764,7 @@
       <c r="AG9" s="7"/>
       <c r="AH9" s="7"/>
       <c r="AI9" s="7" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="AJ9" s="7"/>
       <c r="AK9" s="7" t="s">
@@ -24873,7 +24870,7 @@
       <c r="AG10" s="7"/>
       <c r="AH10" s="7"/>
       <c r="AI10" s="7" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="AJ10" s="7"/>
       <c r="AK10" s="7"/>
@@ -24963,7 +24960,7 @@
       <c r="AG11" s="7"/>
       <c r="AH11" s="7"/>
       <c r="AI11" s="7" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="AJ11" s="7"/>
       <c r="AK11" s="7"/>
@@ -25011,7 +25008,7 @@
         <v>252</v>
       </c>
       <c r="F12" s="26" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="G12" s="4"/>
       <c r="H12" s="4" t="s">
@@ -25390,7 +25387,7 @@
         <v>257</v>
       </c>
       <c r="F17" s="26" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="G17" s="7"/>
       <c r="H17" s="7"/>
@@ -25451,10 +25448,10 @@
         <v>475</v>
       </c>
       <c r="BI17" s="25" t="s">
-        <v>1494</v>
+        <v>1492</v>
       </c>
       <c r="BK17" s="25" t="s">
-        <v>1470</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="18" spans="1:63" ht="120" x14ac:dyDescent="0.25">
@@ -25529,10 +25526,10 @@
         <v>476</v>
       </c>
       <c r="BI18" s="25" t="s">
-        <v>1472</v>
+        <v>1470</v>
       </c>
       <c r="BK18" s="25" t="s">
-        <v>1471</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="19" spans="1:63" ht="135" x14ac:dyDescent="0.25">
@@ -25607,10 +25604,10 @@
         <v>845</v>
       </c>
       <c r="BI19" s="25" t="s">
-        <v>1495</v>
+        <v>1493</v>
       </c>
       <c r="BK19" s="25" t="s">
-        <v>1472</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="20" spans="1:63" ht="105" x14ac:dyDescent="0.25">
@@ -25693,7 +25690,7 @@
       </c>
       <c r="BI20" s="18"/>
       <c r="BK20" s="25" t="s">
-        <v>1473</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="21" spans="1:63" ht="135" x14ac:dyDescent="0.25">
@@ -25768,7 +25765,7 @@
       </c>
       <c r="BI21" s="18"/>
       <c r="BK21" s="25" t="s">
-        <v>1474</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="22" spans="1:63" x14ac:dyDescent="0.25">
@@ -25935,7 +25932,7 @@
         <v>329</v>
       </c>
       <c r="U24" s="4" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="Y24" s="7"/>
       <c r="Z24" s="7"/>
@@ -27040,7 +27037,7 @@
       <c r="AQ41" s="7"/>
       <c r="AR41" s="7"/>
       <c r="AS41" s="7" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
       <c r="AT41" s="7"/>
       <c r="AU41" s="7"/>
@@ -27100,7 +27097,7 @@
       <c r="AQ42" s="7"/>
       <c r="AR42" s="7"/>
       <c r="AS42" s="7" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="AT42" s="7"/>
       <c r="AU42" s="7"/>
@@ -27121,10 +27118,10 @@
     </row>
     <row r="43" spans="1:61" x14ac:dyDescent="0.25">
       <c r="B43" s="7" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="P43" s="5"/>
       <c r="Q43" s="5"/>
@@ -27138,81 +27135,81 @@
     </row>
     <row r="44" spans="1:61" x14ac:dyDescent="0.25">
       <c r="B44" s="7" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="C44" s="7"/>
     </row>
     <row r="45" spans="1:61" x14ac:dyDescent="0.25">
       <c r="B45" s="7" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="C45" s="7"/>
     </row>
     <row r="46" spans="1:61" x14ac:dyDescent="0.25">
       <c r="B46" s="7" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="C46" s="7"/>
     </row>
     <row r="47" spans="1:61" x14ac:dyDescent="0.25">
       <c r="B47" s="7" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="C47" s="7"/>
     </row>
     <row r="48" spans="1:61" x14ac:dyDescent="0.25">
       <c r="B48" s="7" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="C48" s="7"/>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B49" s="7" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="C49" s="7"/>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B50" s="7" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B51" s="7" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="C51" s="7"/>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B52" s="7" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="C52" s="7"/>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B53" s="7" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="C53" s="7"/>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B54" s="7" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="C54" s="7"/>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B55" s="7" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="C55" s="7"/>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B56" s="7" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="C56" s="7"/>
     </row>
@@ -27781,7 +27778,7 @@
         <v>940</v>
       </c>
       <c r="BD3" s="7" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
       <c r="BE3" s="7" t="s">
         <v>1052</v>
@@ -27952,7 +27949,7 @@
       </c>
       <c r="BI4" s="4"/>
       <c r="BJ4" s="4" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="BK4" s="4" t="s">
         <v>568</v>
@@ -28077,10 +28074,10 @@
         <v>349</v>
       </c>
       <c r="BD5" s="26" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
       <c r="BE5" s="25" t="s">
-        <v>1490</v>
+        <v>1488</v>
       </c>
       <c r="BG5" s="4" t="s">
         <v>499</v>
@@ -28090,7 +28087,7 @@
       </c>
       <c r="BI5" s="4"/>
       <c r="BJ5" s="4" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="BK5" s="4"/>
       <c r="BM5" s="4" t="s">
@@ -28114,7 +28111,7 @@
         <v>173</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>246</v>
@@ -28174,7 +28171,7 @@
         <v>525</v>
       </c>
       <c r="AP6" s="7" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="AS6" s="7" t="s">
         <v>523</v>
@@ -28297,7 +28294,7 @@
         <v>494</v>
       </c>
       <c r="AP7" s="7" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="AS7" s="7" t="s">
         <v>526</v>
@@ -28405,7 +28402,7 @@
         <v>1</v>
       </c>
       <c r="AP8" s="7" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="AS8" s="7" t="s">
         <v>528</v>
@@ -28426,17 +28423,17 @@
         <v>364</v>
       </c>
       <c r="BG8" s="18" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="BH8" s="18" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="BI8" s="4"/>
       <c r="BM8" s="18" t="s">
+        <v>1419</v>
+      </c>
+      <c r="BN8" s="18" t="s">
         <v>1421</v>
-      </c>
-      <c r="BN8" s="18" t="s">
-        <v>1423</v>
       </c>
       <c r="BP8" s="7" t="s">
         <v>416</v>
@@ -28498,7 +28495,7 @@
         <v>361</v>
       </c>
       <c r="AP9" s="7" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="AS9" s="7" t="s">
         <v>529</v>
@@ -28585,7 +28582,7 @@
         <v>947</v>
       </c>
       <c r="AP10" s="7" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="AS10" s="7" t="s">
         <v>257</v>
@@ -28660,7 +28657,7 @@
         <v>0</v>
       </c>
       <c r="AP11" s="7" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="AS11" s="7" t="s">
         <v>530</v>
@@ -28687,10 +28684,10 @@
         <v>252</v>
       </c>
       <c r="F12" s="26" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="G12" s="26" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="H12" s="4"/>
       <c r="I12" s="4" t="s">
@@ -28971,10 +28968,10 @@
         <v>257</v>
       </c>
       <c r="F17" s="26" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="G17" s="26" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="R17" s="4"/>
       <c r="S17" s="4"/>
@@ -29007,10 +29004,10 @@
         <v>475</v>
       </c>
       <c r="BQ17" s="25" t="s">
+        <v>1494</v>
+      </c>
+      <c r="BR17" s="25" t="s">
         <v>1496</v>
-      </c>
-      <c r="BR17" s="25" t="s">
-        <v>1498</v>
       </c>
     </row>
     <row r="18" spans="2:70" ht="90" x14ac:dyDescent="0.25">
@@ -29060,10 +29057,10 @@
         <v>476</v>
       </c>
       <c r="BQ18" s="25" t="s">
+        <v>1495</v>
+      </c>
+      <c r="BR18" s="25" t="s">
         <v>1497</v>
-      </c>
-      <c r="BR18" s="25" t="s">
-        <v>1499</v>
       </c>
     </row>
     <row r="19" spans="2:70" ht="90" x14ac:dyDescent="0.25">
@@ -29114,7 +29111,7 @@
       </c>
       <c r="BQ19" s="25"/>
       <c r="BR19" s="25" t="s">
-        <v>1500</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="20" spans="2:70" x14ac:dyDescent="0.25">
@@ -29306,7 +29303,7 @@
         <v>329</v>
       </c>
       <c r="W24" s="4" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="X24" s="4"/>
       <c r="Y24" s="4"/>
@@ -29740,7 +29737,7 @@
       <c r="AC36" s="4"/>
       <c r="AD36" s="4"/>
       <c r="AZ36" s="7" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="37" spans="2:52" x14ac:dyDescent="0.25">
@@ -29773,7 +29770,7 @@
       <c r="AC37" s="4"/>
       <c r="AD37" s="4"/>
       <c r="AZ37" s="7" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="38" spans="2:52" x14ac:dyDescent="0.25">
@@ -29904,46 +29901,46 @@
     </row>
     <row r="43" spans="2:52" x14ac:dyDescent="0.25">
       <c r="B43" s="7" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="Y43" s="4"/>
     </row>
     <row r="44" spans="2:52" x14ac:dyDescent="0.25">
       <c r="B44" s="7" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="Y44" s="4"/>
     </row>
     <row r="45" spans="2:52" x14ac:dyDescent="0.25">
       <c r="B45" s="7" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="Y45" s="4"/>
     </row>
     <row r="46" spans="2:52" x14ac:dyDescent="0.25">
       <c r="B46" s="7" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="Y46" s="4"/>
     </row>
     <row r="47" spans="2:52" x14ac:dyDescent="0.25">
       <c r="B47" s="7" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="Y47" s="4"/>
     </row>
     <row r="48" spans="2:52" x14ac:dyDescent="0.25">
       <c r="B48" s="7" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="Y48" s="4"/>
     </row>
     <row r="49" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B49" s="7" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="Y49" s="4"/>
     </row>
@@ -30525,10 +30522,10 @@
         <v>1129</v>
       </c>
       <c r="AW3" s="7" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
       <c r="AX3" s="7" t="s">
-        <v>1477</v>
+        <v>1475</v>
       </c>
       <c r="AY3" s="18"/>
       <c r="AZ3" s="4" t="s">
@@ -30694,7 +30691,7 @@
       </c>
       <c r="BB4" s="4"/>
       <c r="BC4" s="4" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="BD4" s="4" t="s">
         <v>568</v>
@@ -30821,10 +30818,10 @@
         <v>349</v>
       </c>
       <c r="AW5" s="26" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
       <c r="AX5" s="25" t="s">
-        <v>1490</v>
+        <v>1488</v>
       </c>
       <c r="AY5" s="18"/>
       <c r="AZ5" s="4" t="s">
@@ -30835,7 +30832,7 @@
       </c>
       <c r="BB5" s="4"/>
       <c r="BC5" s="4" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="BD5" s="4"/>
       <c r="BE5" s="18"/>
@@ -30874,7 +30871,7 @@
         <v>173</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>246</v>
@@ -30926,7 +30923,7 @@
         <v>525</v>
       </c>
       <c r="AJ6" s="7" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="AM6" s="7" t="s">
         <v>523</v>
@@ -31054,7 +31051,7 @@
         <v>494</v>
       </c>
       <c r="AJ7" s="7" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="AM7" s="7" t="s">
         <v>526</v>
@@ -31106,7 +31103,7 @@
         <v>467</v>
       </c>
       <c r="BQ7" s="42" t="s">
-        <v>1485</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="8" spans="1:69" ht="30" x14ac:dyDescent="0.25">
@@ -31170,7 +31167,7 @@
         <v>1</v>
       </c>
       <c r="AJ8" s="7" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="AM8" s="7" t="s">
         <v>528</v>
@@ -31192,18 +31189,18 @@
       </c>
       <c r="AY8" s="18"/>
       <c r="AZ8" s="18" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="BA8" s="18" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="BB8" s="4"/>
       <c r="BE8" s="18"/>
       <c r="BF8" s="18" t="s">
+        <v>1419</v>
+      </c>
+      <c r="BG8" s="18" t="s">
         <v>1421</v>
-      </c>
-      <c r="BG8" s="18" t="s">
-        <v>1423</v>
       </c>
       <c r="BI8" s="7" t="s">
         <v>416</v>
@@ -31269,7 +31266,7 @@
         <v>361</v>
       </c>
       <c r="AJ9" s="7" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="AM9" s="7" t="s">
         <v>529</v>
@@ -31303,7 +31300,7 @@
         <v>467</v>
       </c>
       <c r="BN9" s="42" t="s">
-        <v>1485</v>
+        <v>1483</v>
       </c>
       <c r="BP9" s="1" t="s">
         <v>265</v>
@@ -31363,7 +31360,7 @@
         <v>508</v>
       </c>
       <c r="AJ10" s="7" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="AM10" s="7" t="s">
         <v>257</v>
@@ -31445,7 +31442,7 @@
         <v>0</v>
       </c>
       <c r="AJ11" s="7" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="AM11" s="7" t="s">
         <v>530</v>
@@ -31472,7 +31469,7 @@
         <v>1140</v>
       </c>
       <c r="BN11" s="18" t="s">
-        <v>1501</v>
+        <v>1499</v>
       </c>
       <c r="BP11" s="1" t="s">
         <v>1137</v>
@@ -31489,7 +31486,7 @@
         <v>252</v>
       </c>
       <c r="F12" s="26" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="G12" s="4"/>
       <c r="H12" s="4" t="s">
@@ -31597,7 +31594,7 @@
         <v>1143</v>
       </c>
       <c r="BN13" s="36" t="s">
-        <v>1486</v>
+        <v>1484</v>
       </c>
       <c r="BP13" s="1" t="s">
         <v>1173</v>
@@ -31779,7 +31776,7 @@
         <v>257</v>
       </c>
       <c r="F17" s="26" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="Q17" s="4"/>
       <c r="R17" s="4"/>
@@ -31811,22 +31808,22 @@
         <v>475</v>
       </c>
       <c r="BJ17" s="25" t="s">
-        <v>1478</v>
+        <v>1476</v>
       </c>
       <c r="BK17" s="25" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
       <c r="BM17" s="7" t="s">
         <v>1146</v>
       </c>
       <c r="BN17" s="35" t="s">
-        <v>1487</v>
+        <v>1485</v>
       </c>
       <c r="BP17" s="1" t="s">
         <v>1146</v>
       </c>
       <c r="BQ17" s="8" t="s">
-        <v>1506</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="18" spans="2:69" ht="60" x14ac:dyDescent="0.25">
@@ -31871,10 +31868,10 @@
         <v>476</v>
       </c>
       <c r="BJ18" s="25" t="s">
+        <v>1478</v>
+      </c>
+      <c r="BK18" s="25" t="s">
         <v>1480</v>
-      </c>
-      <c r="BK18" s="25" t="s">
-        <v>1482</v>
       </c>
       <c r="BM18" s="7" t="s">
         <v>1148</v>
@@ -31931,22 +31928,22 @@
         <v>845</v>
       </c>
       <c r="BJ19" s="25" t="s">
+        <v>1479</v>
+      </c>
+      <c r="BK19" s="25" t="s">
         <v>1481</v>
-      </c>
-      <c r="BK19" s="25" t="s">
-        <v>1483</v>
       </c>
       <c r="BM19" s="7" t="s">
         <v>1149</v>
       </c>
       <c r="BN19" s="35" t="s">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="BP19" s="1" t="s">
         <v>1140</v>
       </c>
       <c r="BQ19" s="18" t="s">
-        <v>1501</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="20" spans="2:69" ht="16.5" x14ac:dyDescent="0.25">
@@ -32043,13 +32040,13 @@
         <v>1151</v>
       </c>
       <c r="BN21" s="35" t="s">
-        <v>1503</v>
+        <v>1501</v>
       </c>
       <c r="BP21" s="1" t="s">
         <v>1143</v>
       </c>
       <c r="BQ21" s="36" t="s">
-        <v>1486</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="22" spans="2:69" ht="66" x14ac:dyDescent="0.25">
@@ -32091,7 +32088,7 @@
         <v>1152</v>
       </c>
       <c r="BN22" s="35" t="s">
-        <v>1504</v>
+        <v>1502</v>
       </c>
       <c r="BP22" s="1" t="s">
         <v>1148</v>
@@ -32136,13 +32133,13 @@
         <v>1160</v>
       </c>
       <c r="BN23" s="35" t="s">
-        <v>1505</v>
+        <v>1503</v>
       </c>
       <c r="BP23" s="1" t="s">
         <v>1177</v>
       </c>
       <c r="BQ23" s="35" t="s">
-        <v>1502</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="24" spans="2:69" ht="33" x14ac:dyDescent="0.25">
@@ -32163,7 +32160,7 @@
         <v>329</v>
       </c>
       <c r="V24" s="4" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="W24" s="4"/>
       <c r="X24" s="4"/>
@@ -32238,7 +32235,7 @@
         <v>1151</v>
       </c>
       <c r="BQ25" s="35" t="s">
-        <v>1503</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="26" spans="2:69" ht="99" x14ac:dyDescent="0.25">
@@ -32291,7 +32288,7 @@
         <v>1152</v>
       </c>
       <c r="BQ26" s="35" t="s">
-        <v>1504</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="27" spans="2:69" ht="99" x14ac:dyDescent="0.25">
@@ -32334,7 +32331,7 @@
         <v>1160</v>
       </c>
       <c r="BQ27" s="35" t="s">
-        <v>1505</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="28" spans="2:69" ht="30" x14ac:dyDescent="0.25">
@@ -32632,7 +32629,7 @@
       <c r="X36" s="4"/>
       <c r="Y36" s="4"/>
       <c r="AT36" s="7" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
       <c r="BE36" s="18"/>
       <c r="BF36" s="18"/>
@@ -32665,7 +32662,7 @@
       <c r="X37" s="4"/>
       <c r="Y37" s="4"/>
       <c r="AT37" s="7" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="BE37" s="18"/>
       <c r="BF37" s="18"/>
@@ -32793,40 +32790,40 @@
     </row>
     <row r="43" spans="2:69" x14ac:dyDescent="0.25">
       <c r="B43" s="7" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="44" spans="2:69" x14ac:dyDescent="0.25">
       <c r="B44" s="7" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="45" spans="2:69" x14ac:dyDescent="0.25">
       <c r="B45" s="7" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="46" spans="2:69" x14ac:dyDescent="0.25">
       <c r="B46" s="7" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="47" spans="2:69" x14ac:dyDescent="0.25">
       <c r="B47" s="7" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="48" spans="2:69" x14ac:dyDescent="0.25">
       <c r="B48" s="7" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="49" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B49" s="7" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="74" spans="69:69" x14ac:dyDescent="0.25">
@@ -37860,16 +37857,16 @@
         <v>1046</v>
       </c>
       <c r="BH2" s="7" t="s">
-        <v>1465</v>
+        <v>1463</v>
       </c>
       <c r="BI2" s="7" t="s">
         <v>99</v>
       </c>
       <c r="BJ2" s="7" t="s">
-        <v>1465</v>
+        <v>1463</v>
       </c>
       <c r="BK2" s="4" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="BL2" s="4" t="s">
         <v>8</v>
@@ -38015,33 +38012,33 @@
         <v>153</v>
       </c>
       <c r="BD3" s="7" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="BF3" s="7" t="s">
         <v>104</v>
       </c>
       <c r="BG3" s="7" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="BI3" s="7" t="s">
         <v>104</v>
       </c>
       <c r="BJ3" s="7" t="s">
-        <v>1466</v>
+        <v>1464</v>
       </c>
       <c r="BK3" s="4"/>
       <c r="BL3" s="4" t="s">
         <v>74</v>
       </c>
       <c r="BM3" s="4" t="s">
-        <v>1464</v>
+        <v>1462</v>
       </c>
       <c r="BN3" s="1"/>
       <c r="BO3" s="1" t="s">
         <v>153</v>
       </c>
       <c r="BP3" s="1" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="4" spans="1:68" ht="120" x14ac:dyDescent="0.25">
@@ -38082,7 +38079,7 @@
         <v>1078</v>
       </c>
       <c r="R4" s="7" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="S4" s="7" t="s">
         <v>359</v>
@@ -38167,7 +38164,7 @@
         <v>75</v>
       </c>
       <c r="BM4" s="4" t="s">
-        <v>1467</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="5" spans="1:68" ht="45" x14ac:dyDescent="0.25">
@@ -38284,10 +38281,10 @@
       </c>
       <c r="BK5" s="4"/>
       <c r="BL5" s="4" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="BM5" s="4" t="s">
-        <v>1468</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="6" spans="1:68" ht="30" x14ac:dyDescent="0.25">
@@ -38359,10 +38356,10 @@
       </c>
       <c r="BK6" s="4"/>
       <c r="BL6" s="4" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="BM6" s="4" t="s">
-        <v>1469</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="7" spans="1:68" ht="45" x14ac:dyDescent="0.25">
@@ -38422,7 +38419,7 @@
       </c>
       <c r="BK7" s="4"/>
       <c r="BL7" s="4" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="BM7" s="4"/>
     </row>
@@ -38470,17 +38467,17 @@
         <v>0.5</v>
       </c>
       <c r="BF8" s="7" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="BI8" s="7" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="BJ8" s="7" t="s">
-        <v>1461</v>
+        <v>1459</v>
       </c>
       <c r="BK8" s="4"/>
       <c r="BL8" s="4" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="BM8" s="4"/>
     </row>
@@ -38531,13 +38528,13 @@
         <v>1</v>
       </c>
       <c r="BF9" s="7" t="s">
+        <v>1367</v>
+      </c>
+      <c r="BG9" s="7" t="s">
         <v>1368</v>
       </c>
-      <c r="BG9" s="7" t="s">
-        <v>1369</v>
-      </c>
       <c r="BI9" s="7" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="BJ9" s="7" t="s">
         <v>266</v>
@@ -38593,10 +38590,10 @@
         <v>2</v>
       </c>
       <c r="BI10" s="7" t="s">
-        <v>1462</v>
+        <v>1460</v>
       </c>
       <c r="BJ10" s="7" t="s">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="BK10" s="4"/>
       <c r="BL10" s="4"/>
@@ -38737,16 +38734,16 @@
         <v>1016</v>
       </c>
       <c r="AA16" s="7" t="s">
-        <v>1484</v>
+        <v>1482</v>
       </c>
       <c r="AB16" s="7" t="s">
-        <v>1484</v>
+        <v>1482</v>
       </c>
       <c r="AC16" s="7" t="s">
-        <v>1484</v>
+        <v>1482</v>
       </c>
       <c r="AD16" s="7" t="s">
-        <v>1484</v>
+        <v>1482</v>
       </c>
       <c r="BK16" s="4"/>
       <c r="BL16" s="4"/>
@@ -39631,7 +39628,7 @@
         <v>1194</v>
       </c>
       <c r="AV3" s="7" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
       <c r="AW3" s="7" t="s">
         <v>1198</v>
@@ -39784,7 +39781,7 @@
       </c>
       <c r="BA4" s="4"/>
       <c r="BB4" s="4" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="BC4" s="4" t="s">
         <v>568</v>
@@ -39897,10 +39894,10 @@
         <v>349</v>
       </c>
       <c r="AV5" s="26" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
       <c r="AW5" s="25" t="s">
-        <v>1490</v>
+        <v>1488</v>
       </c>
       <c r="AY5" s="4" t="s">
         <v>499</v>
@@ -39910,7 +39907,7 @@
       </c>
       <c r="BA5" s="4"/>
       <c r="BB5" s="4" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="BC5" s="4"/>
       <c r="BE5" s="4" t="s">
@@ -39939,7 +39936,7 @@
         <v>173</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>246</v>
@@ -39991,7 +39988,7 @@
         <v>525</v>
       </c>
       <c r="AJ6" s="7" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="AM6" s="7" t="s">
         <v>523</v>
@@ -40104,7 +40101,7 @@
         <v>494</v>
       </c>
       <c r="AJ7" s="7" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="AM7" s="7" t="s">
         <v>526</v>
@@ -40143,7 +40140,7 @@
         <v>467</v>
       </c>
       <c r="BL7" s="7" t="s">
-        <v>1485</v>
+        <v>1483</v>
       </c>
       <c r="BM7" s="18"/>
     </row>
@@ -40208,7 +40205,7 @@
         <v>1</v>
       </c>
       <c r="AJ8" s="7" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="AM8" s="7" t="s">
         <v>528</v>
@@ -40226,16 +40223,16 @@
         <v>364</v>
       </c>
       <c r="AY8" s="18" t="s">
+        <v>1419</v>
+      </c>
+      <c r="AZ8" s="18" t="s">
+        <v>1420</v>
+      </c>
+      <c r="BE8" s="18" t="s">
+        <v>1419</v>
+      </c>
+      <c r="BF8" s="18" t="s">
         <v>1421</v>
-      </c>
-      <c r="AZ8" s="18" t="s">
-        <v>1422</v>
-      </c>
-      <c r="BE8" s="18" t="s">
-        <v>1421</v>
-      </c>
-      <c r="BF8" s="18" t="s">
-        <v>1423</v>
       </c>
       <c r="BH8" s="7" t="s">
         <v>416</v>
@@ -40295,7 +40292,7 @@
         <v>361</v>
       </c>
       <c r="AJ9" s="7" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="AM9" s="7" t="s">
         <v>529</v>
@@ -40375,7 +40372,7 @@
         <v>508</v>
       </c>
       <c r="AJ10" s="7" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="AM10" s="7" t="s">
         <v>257</v>
@@ -40443,7 +40440,7 @@
         <v>0</v>
       </c>
       <c r="AJ11" s="7" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="AM11" s="7" t="s">
         <v>530</v>
@@ -40729,13 +40726,13 @@
         <v>475</v>
       </c>
       <c r="BI17" s="25" t="s">
-        <v>1507</v>
+        <v>1505</v>
       </c>
       <c r="BK17" s="7" t="s">
         <v>1146</v>
       </c>
       <c r="BL17" s="25" t="s">
-        <v>1510</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="18" spans="2:64" ht="45" x14ac:dyDescent="0.25">
@@ -40775,7 +40772,7 @@
         <v>476</v>
       </c>
       <c r="BI18" s="25" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="BK18" s="7" t="s">
         <v>1138</v>
@@ -40786,10 +40783,10 @@
     </row>
     <row r="19" spans="2:64" ht="45" x14ac:dyDescent="0.25">
       <c r="B19" s="22" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>258</v>
@@ -40818,13 +40815,13 @@
         <v>845</v>
       </c>
       <c r="BI19" s="7" t="s">
-        <v>1509</v>
+        <v>1507</v>
       </c>
       <c r="BK19" s="7" t="s">
         <v>1140</v>
       </c>
       <c r="BL19" s="18" t="s">
-        <v>1511</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="20" spans="2:64" ht="30" x14ac:dyDescent="0.25">
@@ -40858,7 +40855,7 @@
         <v>274</v>
       </c>
       <c r="AS20" s="7" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
       <c r="BK20" s="7" t="s">
         <v>1141</v>
@@ -40894,13 +40891,13 @@
       <c r="X21" s="4"/>
       <c r="Y21" s="4"/>
       <c r="AS21" s="7" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="BK21" s="7" t="s">
         <v>1143</v>
       </c>
       <c r="BL21" s="36" t="s">
-        <v>1512</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="22" spans="2:64" ht="30" x14ac:dyDescent="0.25">
@@ -40972,7 +40969,7 @@
         <v>1177</v>
       </c>
       <c r="BL23" s="35" t="s">
-        <v>1502</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="24" spans="2:64" ht="33" x14ac:dyDescent="0.25">
@@ -40993,7 +40990,7 @@
         <v>329</v>
       </c>
       <c r="V24" s="4" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="W24" s="4"/>
       <c r="X24" s="4"/>
@@ -41052,7 +41049,7 @@
         <v>1151</v>
       </c>
       <c r="BL25" s="35" t="s">
-        <v>1513</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="26" spans="2:64" ht="115.5" x14ac:dyDescent="0.25">
@@ -41096,7 +41093,7 @@
         <v>1152</v>
       </c>
       <c r="BL26" s="35" t="s">
-        <v>1514</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="27" spans="2:64" ht="132" x14ac:dyDescent="0.25">
@@ -41132,7 +41129,7 @@
         <v>1160</v>
       </c>
       <c r="BL27" s="35" t="s">
-        <v>1515</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="28" spans="2:64" ht="30" x14ac:dyDescent="0.25">
@@ -41538,34 +41535,34 @@
     </row>
     <row r="44" spans="2:64" x14ac:dyDescent="0.25">
       <c r="B44" s="29" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="BK44" s="18"/>
     </row>
     <row r="45" spans="2:64" x14ac:dyDescent="0.25">
       <c r="B45" s="1" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="BK45" s="18"/>
     </row>
     <row r="46" spans="2:64" x14ac:dyDescent="0.25">
       <c r="B46" s="1" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="47" spans="2:64" x14ac:dyDescent="0.25">
       <c r="B47" s="1" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="48" spans="2:64" x14ac:dyDescent="0.25">
       <c r="B48" s="1" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="49" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B49" s="1" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="71" spans="62:62" x14ac:dyDescent="0.25">
@@ -42718,7 +42715,7 @@
         <v>627</v>
       </c>
       <c r="Z10" s="40" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="AC10" s="1" t="s">
         <v>585</v>
@@ -42946,7 +42943,7 @@
         <v>137</v>
       </c>
       <c r="AM15" s="1" t="s">
-        <v>1424</v>
+        <v>1422</v>
       </c>
       <c r="AO15" s="1" t="s">
         <v>139</v>
@@ -43176,7 +43173,7 @@
       <c r="BD31" s="5"/>
       <c r="BG31" s="5"/>
       <c r="BH31" s="5" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="BI31" s="5" t="b">
         <v>0</v>
@@ -43186,7 +43183,7 @@
       <c r="BE32" s="5"/>
       <c r="BF32" s="5"/>
       <c r="BH32" s="4" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="BI32" s="5" t="b">
         <v>0</v>
@@ -43194,7 +43191,7 @@
     </row>
     <row r="33" spans="60:61" ht="30" x14ac:dyDescent="0.25">
       <c r="BH33" s="4" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="BI33" s="4">
         <v>0</v>
@@ -43202,7 +43199,7 @@
     </row>
     <row r="34" spans="60:61" ht="30" x14ac:dyDescent="0.25">
       <c r="BH34" s="4" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
       <c r="BI34" s="4">
         <v>0</v>
@@ -43210,7 +43207,7 @@
     </row>
     <row r="35" spans="60:61" ht="30" x14ac:dyDescent="0.25">
       <c r="BH35" s="4" t="s">
-        <v>1388</v>
+        <v>1386</v>
       </c>
       <c r="BI35" s="5" t="b">
         <v>0</v>
@@ -43218,7 +43215,7 @@
     </row>
     <row r="36" spans="60:61" ht="30" x14ac:dyDescent="0.25">
       <c r="BH36" s="4" t="s">
-        <v>1389</v>
+        <v>1387</v>
       </c>
       <c r="BI36" s="5" t="b">
         <v>0</v>
@@ -43226,7 +43223,7 @@
     </row>
     <row r="37" spans="60:61" x14ac:dyDescent="0.25">
       <c r="BH37" s="4" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
       <c r="BI37" s="4">
         <v>0</v>
@@ -43234,7 +43231,7 @@
     </row>
     <row r="38" spans="60:61" x14ac:dyDescent="0.25">
       <c r="BH38" s="4" t="s">
-        <v>1391</v>
+        <v>1389</v>
       </c>
       <c r="BI38" s="4">
         <v>0</v>
@@ -43763,10 +43760,10 @@
         <v>1205</v>
       </c>
       <c r="AV3" s="7" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
       <c r="AW3" s="7" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="AY3" s="4" t="s">
         <v>74</v>
@@ -43921,7 +43918,7 @@
       </c>
       <c r="BA4" s="4"/>
       <c r="BB4" s="4" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="BC4" s="4" t="s">
         <v>568</v>
@@ -44039,10 +44036,10 @@
         <v>349</v>
       </c>
       <c r="AV5" s="26" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
       <c r="AW5" s="25" t="s">
-        <v>1490</v>
+        <v>1488</v>
       </c>
       <c r="AY5" s="4" t="s">
         <v>499</v>
@@ -44052,7 +44049,7 @@
       </c>
       <c r="BA5" s="4"/>
       <c r="BB5" s="4" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="BC5" s="4"/>
       <c r="BE5" s="4" t="s">
@@ -44085,7 +44082,7 @@
         <v>173</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>246</v>
@@ -44137,7 +44134,7 @@
         <v>525</v>
       </c>
       <c r="AJ6" s="7" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="AM6" s="7" t="s">
         <v>523</v>
@@ -44255,7 +44252,7 @@
         <v>494</v>
       </c>
       <c r="AJ7" s="7" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="AM7" s="7" t="s">
         <v>526</v>
@@ -44299,7 +44296,7 @@
         <v>467</v>
       </c>
       <c r="BO7" s="7" t="s">
-        <v>1485</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="8" spans="1:67" ht="30" x14ac:dyDescent="0.25">
@@ -44363,7 +44360,7 @@
         <v>1</v>
       </c>
       <c r="AJ8" s="7" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="AM8" s="7" t="s">
         <v>528</v>
@@ -44381,16 +44378,16 @@
         <v>364</v>
       </c>
       <c r="AY8" s="18" t="s">
+        <v>1419</v>
+      </c>
+      <c r="AZ8" s="18" t="s">
+        <v>1420</v>
+      </c>
+      <c r="BE8" s="18" t="s">
+        <v>1419</v>
+      </c>
+      <c r="BF8" s="18" t="s">
         <v>1421</v>
-      </c>
-      <c r="AZ8" s="18" t="s">
-        <v>1422</v>
-      </c>
-      <c r="BE8" s="18" t="s">
-        <v>1421</v>
-      </c>
-      <c r="BF8" s="18" t="s">
-        <v>1423</v>
       </c>
       <c r="BH8" s="7" t="s">
         <v>416</v>
@@ -44458,7 +44455,7 @@
         <v>361</v>
       </c>
       <c r="AJ9" s="7" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="AM9" s="7" t="s">
         <v>529</v>
@@ -44484,7 +44481,7 @@
         <v>467</v>
       </c>
       <c r="BL9" s="42" t="s">
-        <v>1485</v>
+        <v>1483</v>
       </c>
       <c r="BM9" s="18"/>
       <c r="BN9" s="7" t="s">
@@ -44546,7 +44543,7 @@
         <v>508</v>
       </c>
       <c r="AJ10" s="7" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="AM10" s="7" t="s">
         <v>257</v>
@@ -44622,7 +44619,7 @@
         <v>0</v>
       </c>
       <c r="AJ11" s="7" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="AM11" s="7" t="s">
         <v>530</v>
@@ -44642,7 +44639,7 @@
         <v>1140</v>
       </c>
       <c r="BL11" s="18" t="s">
-        <v>1511</v>
+        <v>1509</v>
       </c>
       <c r="BM11" s="18"/>
       <c r="BN11" s="7" t="s">
@@ -44759,7 +44756,7 @@
         <v>1143</v>
       </c>
       <c r="BL13" s="36" t="s">
-        <v>1519</v>
+        <v>1517</v>
       </c>
       <c r="BM13" s="18"/>
       <c r="BN13" s="7" t="s">
@@ -44953,21 +44950,21 @@
         <v>475</v>
       </c>
       <c r="BI17" s="25" t="s">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="BJ17" s="18"/>
       <c r="BK17" s="7" t="s">
         <v>1146</v>
       </c>
       <c r="BL17" s="35" t="s">
-        <v>1520</v>
+        <v>1518</v>
       </c>
       <c r="BM17" s="18"/>
       <c r="BN17" s="7" t="s">
         <v>1146</v>
       </c>
       <c r="BO17" s="25" t="s">
-        <v>1524</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="18" spans="2:67" ht="75" x14ac:dyDescent="0.25">
@@ -45007,7 +45004,7 @@
         <v>476</v>
       </c>
       <c r="BI18" s="25" t="s">
-        <v>1517</v>
+        <v>1515</v>
       </c>
       <c r="BJ18" s="18"/>
       <c r="BK18" s="7" t="s">
@@ -45026,10 +45023,10 @@
     </row>
     <row r="19" spans="2:67" ht="115.5" x14ac:dyDescent="0.25">
       <c r="B19" s="22" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>258</v>
@@ -45058,21 +45055,21 @@
         <v>845</v>
       </c>
       <c r="BI19" s="25" t="s">
-        <v>1518</v>
+        <v>1516</v>
       </c>
       <c r="BJ19" s="18"/>
       <c r="BK19" s="7" t="s">
         <v>1149</v>
       </c>
       <c r="BL19" s="35" t="s">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="BM19" s="18"/>
       <c r="BN19" s="7" t="s">
         <v>1140</v>
       </c>
       <c r="BO19" s="18" t="s">
-        <v>1511</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="20" spans="2:67" ht="33" x14ac:dyDescent="0.25">
@@ -45106,7 +45103,7 @@
         <v>274</v>
       </c>
       <c r="AS20" s="7" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
       <c r="BI20" s="25"/>
       <c r="BJ20" s="18"/>
@@ -45151,7 +45148,7 @@
       <c r="X21" s="4"/>
       <c r="Y21" s="4"/>
       <c r="AS21" s="7" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="BI21" s="25"/>
       <c r="BJ21" s="18"/>
@@ -45159,14 +45156,14 @@
         <v>1151</v>
       </c>
       <c r="BL21" s="35" t="s">
-        <v>1521</v>
+        <v>1519</v>
       </c>
       <c r="BM21" s="18"/>
       <c r="BN21" s="7" t="s">
         <v>1143</v>
       </c>
       <c r="BO21" s="36" t="s">
-        <v>1519</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="22" spans="2:67" ht="115.5" x14ac:dyDescent="0.25">
@@ -45204,7 +45201,7 @@
         <v>1152</v>
       </c>
       <c r="BL22" s="35" t="s">
-        <v>1522</v>
+        <v>1520</v>
       </c>
       <c r="BM22" s="18"/>
       <c r="BN22" s="7" t="s">
@@ -45248,14 +45245,14 @@
         <v>1160</v>
       </c>
       <c r="BL23" s="35" t="s">
-        <v>1523</v>
+        <v>1521</v>
       </c>
       <c r="BM23" s="18"/>
       <c r="BN23" s="7" t="s">
         <v>1177</v>
       </c>
       <c r="BO23" s="35" t="s">
-        <v>1502</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="24" spans="2:67" ht="33" x14ac:dyDescent="0.25">
@@ -45276,7 +45273,7 @@
         <v>329</v>
       </c>
       <c r="V24" s="4" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="W24" s="4"/>
       <c r="X24" s="4"/>
@@ -45348,7 +45345,7 @@
         <v>1151</v>
       </c>
       <c r="BO25" s="35" t="s">
-        <v>1521</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="26" spans="2:67" ht="115.5" x14ac:dyDescent="0.25">
@@ -45400,7 +45397,7 @@
         <v>1152</v>
       </c>
       <c r="BO26" s="35" t="s">
-        <v>1522</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="27" spans="2:67" ht="132" x14ac:dyDescent="0.25">
@@ -45442,7 +45439,7 @@
         <v>1160</v>
       </c>
       <c r="BO27" s="35" t="s">
-        <v>1523</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="28" spans="2:67" ht="30" x14ac:dyDescent="0.25">
@@ -45849,32 +45846,32 @@
     </row>
     <row r="44" spans="2:67" x14ac:dyDescent="0.25">
       <c r="B44" s="29" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="45" spans="2:67" x14ac:dyDescent="0.25">
       <c r="B45" s="1" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="46" spans="2:67" x14ac:dyDescent="0.25">
       <c r="B46" s="1" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="47" spans="2:67" x14ac:dyDescent="0.25">
       <c r="B47" s="1" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="48" spans="2:67" x14ac:dyDescent="0.25">
       <c r="B48" s="1" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="49" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B49" s="1" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
     </row>
   </sheetData>
@@ -46583,7 +46580,7 @@
         <v>1219</v>
       </c>
       <c r="BD3" s="7" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
       <c r="BE3" s="7" t="s">
         <v>1226</v>
@@ -46620,7 +46617,7 @@
         <v>1124</v>
       </c>
       <c r="BV3" s="7" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
       <c r="BW3" s="7" t="s">
         <v>1227</v>
@@ -46796,7 +46793,7 @@
       </c>
       <c r="BI4" s="4"/>
       <c r="BJ4" s="4" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="BK4" s="4" t="s">
         <v>568</v>
@@ -46834,7 +46831,7 @@
       </c>
       <c r="CA4" s="4"/>
       <c r="CB4" s="4" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="CC4" s="4" t="s">
         <v>568</v>
@@ -46967,10 +46964,10 @@
         <v>349</v>
       </c>
       <c r="BD5" s="26" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
       <c r="BE5" s="25" t="s">
-        <v>1490</v>
+        <v>1488</v>
       </c>
       <c r="BG5" s="4" t="s">
         <v>499</v>
@@ -46980,7 +46977,7 @@
       </c>
       <c r="BI5" s="4"/>
       <c r="BJ5" s="4" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="BK5" s="4"/>
       <c r="BM5" s="4" t="s">
@@ -47002,10 +46999,10 @@
         <v>1220</v>
       </c>
       <c r="BV5" s="26" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
       <c r="BW5" s="25" t="s">
-        <v>1490</v>
+        <v>1488</v>
       </c>
       <c r="BY5" s="4" t="s">
         <v>499</v>
@@ -47015,7 +47012,7 @@
       </c>
       <c r="CA5" s="4"/>
       <c r="CB5" s="4" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="CC5" s="4"/>
       <c r="CE5" s="4" t="s">
@@ -47100,7 +47097,7 @@
         <v>525</v>
       </c>
       <c r="AP6" s="7" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="AS6" s="7" t="s">
         <v>523</v>
@@ -47151,7 +47148,7 @@
         <v>467</v>
       </c>
       <c r="BT6" s="7" t="s">
-        <v>1485</v>
+        <v>1483</v>
       </c>
       <c r="BY6" s="4" t="s">
         <v>500</v>
@@ -47178,13 +47175,13 @@
         <v>467</v>
       </c>
       <c r="CL6" s="7" t="s">
-        <v>1485</v>
+        <v>1483</v>
       </c>
       <c r="CN6" s="7" t="s">
         <v>467</v>
       </c>
       <c r="CO6" s="7" t="s">
-        <v>1485</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="7" spans="1:93" x14ac:dyDescent="0.25">
@@ -47266,7 +47263,7 @@
         <v>494</v>
       </c>
       <c r="AP7" s="7" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="AS7" s="7" t="s">
         <v>526</v>
@@ -47410,7 +47407,7 @@
         <v>1</v>
       </c>
       <c r="AP8" s="7" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="AS8" s="7" t="s">
         <v>528</v>
@@ -47431,17 +47428,17 @@
         <v>364</v>
       </c>
       <c r="BG8" s="18" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="BH8" s="18" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="BI8" s="4"/>
       <c r="BM8" s="18" t="s">
+        <v>1419</v>
+      </c>
+      <c r="BN8" s="18" t="s">
         <v>1421</v>
-      </c>
-      <c r="BN8" s="18" t="s">
-        <v>1423</v>
       </c>
       <c r="BP8" s="7" t="s">
         <v>416</v>
@@ -47450,17 +47447,17 @@
         <v>265</v>
       </c>
       <c r="BY8" s="18" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="BZ8" s="18" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="CA8" s="4"/>
       <c r="CE8" s="18" t="s">
+        <v>1419</v>
+      </c>
+      <c r="CF8" s="18" t="s">
         <v>1421</v>
-      </c>
-      <c r="CF8" s="18" t="s">
-        <v>1423</v>
       </c>
       <c r="CH8" s="7" t="s">
         <v>416</v>
@@ -47525,7 +47522,7 @@
         <v>361</v>
       </c>
       <c r="AP9" s="7" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="AS9" s="7" t="s">
         <v>529</v>
@@ -47625,7 +47622,7 @@
         <v>491</v>
       </c>
       <c r="AP10" s="7" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="AS10" s="7" t="s">
         <v>257</v>
@@ -47716,7 +47713,7 @@
         <v>0</v>
       </c>
       <c r="AP11" s="7" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="AS11" s="7" t="s">
         <v>530</v>
@@ -48028,7 +48025,7 @@
         <v>1146</v>
       </c>
       <c r="BT16" s="25" t="s">
-        <v>1525</v>
+        <v>1523</v>
       </c>
       <c r="BU16" s="26"/>
       <c r="BV16" s="26"/>
@@ -48049,13 +48046,13 @@
         <v>1146</v>
       </c>
       <c r="CL16" s="25" t="s">
-        <v>1538</v>
+        <v>1536</v>
       </c>
       <c r="CN16" s="7" t="s">
         <v>1146</v>
       </c>
       <c r="CO16" s="25" t="s">
-        <v>1538</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="17" spans="2:93" ht="90" x14ac:dyDescent="0.25">
@@ -48092,7 +48089,7 @@
         <v>475</v>
       </c>
       <c r="BQ17" s="25" t="s">
-        <v>1528</v>
+        <v>1526</v>
       </c>
       <c r="BS17" s="7" t="s">
         <v>1138</v>
@@ -48104,7 +48101,7 @@
         <v>475</v>
       </c>
       <c r="CI17" s="25" t="s">
-        <v>1528</v>
+        <v>1526</v>
       </c>
       <c r="CK17" s="7" t="s">
         <v>1138</v>
@@ -48153,39 +48150,39 @@
         <v>476</v>
       </c>
       <c r="BQ18" s="25" t="s">
-        <v>1529</v>
+        <v>1527</v>
       </c>
       <c r="BS18" s="7" t="s">
         <v>1140</v>
       </c>
       <c r="BT18" s="7" t="s">
-        <v>1526</v>
+        <v>1524</v>
       </c>
       <c r="CH18" s="7" t="s">
         <v>476</v>
       </c>
       <c r="CI18" s="25" t="s">
-        <v>1536</v>
+        <v>1534</v>
       </c>
       <c r="CK18" s="7" t="s">
         <v>1140</v>
       </c>
       <c r="CL18" s="7" t="s">
-        <v>1539</v>
+        <v>1537</v>
       </c>
       <c r="CN18" s="7" t="s">
         <v>1140</v>
       </c>
       <c r="CO18" s="7" t="s">
-        <v>1539</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="19" spans="2:93" ht="90" x14ac:dyDescent="0.25">
       <c r="B19" s="22" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>258</v>
@@ -48208,7 +48205,7 @@
         <v>845</v>
       </c>
       <c r="BQ19" s="25" t="s">
-        <v>1530</v>
+        <v>1528</v>
       </c>
       <c r="BS19" s="7" t="s">
         <v>1141</v>
@@ -48220,7 +48217,7 @@
         <v>845</v>
       </c>
       <c r="CI19" s="25" t="s">
-        <v>1530</v>
+        <v>1528</v>
       </c>
       <c r="CK19" s="7" t="s">
         <v>1141</v>
@@ -48263,37 +48260,37 @@
         <v>274</v>
       </c>
       <c r="AZ20" s="7" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
       <c r="BP20" s="7" t="s">
         <v>916</v>
       </c>
       <c r="BQ20" s="25" t="s">
-        <v>1531</v>
+        <v>1529</v>
       </c>
       <c r="BS20" s="7" t="s">
         <v>1143</v>
       </c>
       <c r="BT20" s="25" t="s">
-        <v>1527</v>
+        <v>1525</v>
       </c>
       <c r="CH20" s="7" t="s">
         <v>916</v>
       </c>
       <c r="CI20" s="25" t="s">
-        <v>1537</v>
+        <v>1535</v>
       </c>
       <c r="CK20" s="7" t="s">
         <v>1143</v>
       </c>
       <c r="CL20" s="25" t="s">
-        <v>1540</v>
+        <v>1538</v>
       </c>
       <c r="CN20" s="7" t="s">
         <v>1143</v>
       </c>
       <c r="CO20" s="25" t="s">
-        <v>1540</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="21" spans="2:93" ht="30" x14ac:dyDescent="0.25">
@@ -48321,7 +48318,7 @@
       </c>
       <c r="AD21" s="4"/>
       <c r="AZ21" s="7" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="BS21" s="7" t="s">
         <v>1148</v>
@@ -48455,10 +48452,10 @@
         <v>329</v>
       </c>
       <c r="Y24" s="4" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="Z24" s="4" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="AD24" s="4"/>
       <c r="AZ24" s="7" t="s">
@@ -48474,19 +48471,19 @@
         <v>1151</v>
       </c>
       <c r="BT24" s="35" t="s">
-        <v>1532</v>
+        <v>1530</v>
       </c>
       <c r="CK24" s="7" t="s">
         <v>1151</v>
       </c>
       <c r="CL24" s="25" t="s">
-        <v>1532</v>
+        <v>1530</v>
       </c>
       <c r="CN24" s="7" t="s">
         <v>1151</v>
       </c>
       <c r="CO24" s="25" t="s">
-        <v>1532</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="25" spans="2:93" ht="82.5" x14ac:dyDescent="0.25">
@@ -48532,7 +48529,7 @@
         <v>1152</v>
       </c>
       <c r="BT25" s="35" t="s">
-        <v>1533</v>
+        <v>1531</v>
       </c>
       <c r="BU25" s="25"/>
       <c r="BV25" s="25"/>
@@ -48547,13 +48544,13 @@
         <v>1152</v>
       </c>
       <c r="CL25" s="25" t="s">
-        <v>1533</v>
+        <v>1531</v>
       </c>
       <c r="CN25" s="7" t="s">
         <v>1152</v>
       </c>
       <c r="CO25" s="25" t="s">
-        <v>1533</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="26" spans="2:93" ht="82.5" x14ac:dyDescent="0.25">
@@ -48596,7 +48593,7 @@
         <v>1160</v>
       </c>
       <c r="BT26" s="35" t="s">
-        <v>1534</v>
+        <v>1532</v>
       </c>
       <c r="BU26" s="25"/>
       <c r="BV26" s="25"/>
@@ -48611,13 +48608,13 @@
         <v>1160</v>
       </c>
       <c r="CL26" s="25" t="s">
-        <v>1541</v>
+        <v>1539</v>
       </c>
       <c r="CN26" s="7" t="s">
         <v>1160</v>
       </c>
       <c r="CO26" s="25" t="s">
-        <v>1541</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="27" spans="2:93" ht="82.5" x14ac:dyDescent="0.25">
@@ -48651,19 +48648,19 @@
         <v>1169</v>
       </c>
       <c r="BT27" s="35" t="s">
-        <v>1535</v>
+        <v>1533</v>
       </c>
       <c r="CK27" s="7" t="s">
         <v>1169</v>
       </c>
       <c r="CL27" s="25" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="CN27" s="7" t="s">
         <v>1169</v>
       </c>
       <c r="CO27" s="25" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="28" spans="2:93" ht="30" x14ac:dyDescent="0.25">
@@ -49032,42 +49029,42 @@
     </row>
     <row r="44" spans="2:93" x14ac:dyDescent="0.25">
       <c r="B44" s="29" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="R44" s="7"/>
       <c r="AD44" s="4"/>
     </row>
     <row r="45" spans="2:93" x14ac:dyDescent="0.25">
       <c r="B45" s="1" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="R45" s="7"/>
       <c r="AD45" s="4"/>
     </row>
     <row r="46" spans="2:93" x14ac:dyDescent="0.25">
       <c r="B46" s="1" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="R46" s="7"/>
       <c r="AD46" s="4"/>
     </row>
     <row r="47" spans="2:93" x14ac:dyDescent="0.25">
       <c r="B47" s="1" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="R47" s="7"/>
       <c r="AD47" s="4"/>
     </row>
     <row r="48" spans="2:93" x14ac:dyDescent="0.25">
       <c r="B48" s="1" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="R48" s="7"/>
       <c r="AD48" s="4"/>
     </row>
     <row r="49" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B49" s="1" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
     </row>
   </sheetData>
@@ -49809,7 +49806,7 @@
       </c>
       <c r="BC3" s="7"/>
       <c r="BD3" s="7" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
       <c r="BE3" s="7" t="s">
         <v>1312</v>
@@ -49849,7 +49846,7 @@
       </c>
       <c r="BU3" s="7"/>
       <c r="BV3" s="7" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
       <c r="BW3" s="7" t="s">
         <v>1313</v>
@@ -50041,7 +50038,7 @@
       </c>
       <c r="BI4" s="4"/>
       <c r="BJ4" s="4" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="BK4" s="4" t="s">
         <v>568</v>
@@ -50081,7 +50078,7 @@
       </c>
       <c r="CA4" s="4"/>
       <c r="CB4" s="4" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="CC4" s="4" t="s">
         <v>568</v>
@@ -50237,10 +50234,10 @@
       <c r="BB5" s="7"/>
       <c r="BC5" s="7"/>
       <c r="BD5" s="26" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
       <c r="BE5" s="25" t="s">
-        <v>1490</v>
+        <v>1488</v>
       </c>
       <c r="BG5" s="4" t="s">
         <v>499</v>
@@ -50250,7 +50247,7 @@
       </c>
       <c r="BI5" s="4"/>
       <c r="BJ5" s="4" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="BK5" s="4"/>
       <c r="BM5" s="4" t="s">
@@ -50275,10 +50272,10 @@
       </c>
       <c r="BU5" s="7"/>
       <c r="BV5" s="26" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
       <c r="BW5" s="25" t="s">
-        <v>1490</v>
+        <v>1488</v>
       </c>
       <c r="BY5" s="4" t="s">
         <v>499</v>
@@ -50288,7 +50285,7 @@
       </c>
       <c r="CA5" s="4"/>
       <c r="CB5" s="4" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="CC5" s="4"/>
       <c r="CE5" s="4" t="s">
@@ -50394,7 +50391,7 @@
       <c r="AN6" s="7"/>
       <c r="AO6" s="7"/>
       <c r="AP6" s="7" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="AQ6" s="7"/>
       <c r="AR6" s="7"/>
@@ -50454,7 +50451,7 @@
         <v>467</v>
       </c>
       <c r="BT6" s="18" t="s">
-        <v>1485</v>
+        <v>1483</v>
       </c>
       <c r="BU6" s="7"/>
       <c r="BV6" s="7"/>
@@ -50486,14 +50483,14 @@
         <v>467</v>
       </c>
       <c r="CL6" s="7" t="s">
-        <v>1485</v>
+        <v>1483</v>
       </c>
       <c r="CM6" s="7"/>
       <c r="CN6" s="7" t="s">
         <v>467</v>
       </c>
       <c r="CO6" s="7" t="s">
-        <v>1485</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="7" spans="1:93" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -50587,7 +50584,7 @@
       <c r="AN7" s="7"/>
       <c r="AO7" s="7"/>
       <c r="AP7" s="7" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="AQ7" s="7"/>
       <c r="AR7" s="7"/>
@@ -50766,7 +50763,7 @@
       <c r="AN8" s="7"/>
       <c r="AO8" s="7"/>
       <c r="AP8" s="7" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="AQ8" s="7"/>
       <c r="AR8" s="7"/>
@@ -50796,19 +50793,19 @@
       <c r="BD8" s="7"/>
       <c r="BE8" s="7"/>
       <c r="BG8" s="18" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="BH8" s="18" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="BI8" s="4"/>
       <c r="BJ8" s="7"/>
       <c r="BK8" s="7"/>
       <c r="BM8" s="18" t="s">
+        <v>1419</v>
+      </c>
+      <c r="BN8" s="18" t="s">
         <v>1421</v>
-      </c>
-      <c r="BN8" s="18" t="s">
-        <v>1423</v>
       </c>
       <c r="BO8" s="7"/>
       <c r="BP8" s="7" t="s">
@@ -50822,19 +50819,19 @@
       <c r="BV8" s="7"/>
       <c r="BW8" s="7"/>
       <c r="BY8" s="18" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="BZ8" s="18" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="CA8" s="4"/>
       <c r="CB8" s="7"/>
       <c r="CC8" s="7"/>
       <c r="CE8" s="18" t="s">
+        <v>1419</v>
+      </c>
+      <c r="CF8" s="18" t="s">
         <v>1421</v>
-      </c>
-      <c r="CF8" s="18" t="s">
-        <v>1423</v>
       </c>
       <c r="CG8" s="7"/>
       <c r="CH8" s="7" t="s">
@@ -50919,7 +50916,7 @@
       <c r="AN9" s="7"/>
       <c r="AO9" s="7"/>
       <c r="AP9" s="7" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="AQ9" s="7"/>
       <c r="AR9" s="7"/>
@@ -51058,7 +51055,7 @@
       <c r="AN10" s="7"/>
       <c r="AO10" s="7"/>
       <c r="AP10" s="7" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="AQ10" s="7"/>
       <c r="AR10" s="7"/>
@@ -51187,7 +51184,7 @@
       <c r="AN11" s="7"/>
       <c r="AO11" s="7"/>
       <c r="AP11" s="7" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="AQ11" s="7"/>
       <c r="AR11" s="7"/>
@@ -51805,7 +51802,7 @@
         <v>1146</v>
       </c>
       <c r="BT16" s="25" t="s">
-        <v>1549</v>
+        <v>1547</v>
       </c>
       <c r="BU16" s="26"/>
       <c r="BV16" s="26"/>
@@ -51827,13 +51824,13 @@
         <v>1146</v>
       </c>
       <c r="CL16" s="25" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="CN16" s="7" t="s">
         <v>1146</v>
       </c>
       <c r="CO16" s="25" t="s">
-        <v>1561</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="17" spans="1:93" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -51923,7 +51920,7 @@
         <v>475</v>
       </c>
       <c r="BQ17" s="25" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="BS17" s="7" t="s">
         <v>1138</v>
@@ -51945,7 +51942,7 @@
         <v>475</v>
       </c>
       <c r="CI17" s="25" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="CK17" s="7" t="s">
         <v>1138</v>
@@ -52045,13 +52042,13 @@
         <v>476</v>
       </c>
       <c r="BQ18" s="25" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="BS18" s="7" t="s">
         <v>1140</v>
       </c>
       <c r="BT18" s="18" t="s">
-        <v>1547</v>
+        <v>1545</v>
       </c>
       <c r="BU18" s="7"/>
       <c r="BV18" s="7"/>
@@ -52067,28 +52064,28 @@
         <v>476</v>
       </c>
       <c r="CI18" s="25" t="s">
-        <v>1554</v>
+        <v>1552</v>
       </c>
       <c r="CK18" s="7" t="s">
         <v>1140</v>
       </c>
       <c r="CL18" s="7" t="s">
-        <v>1558</v>
+        <v>1556</v>
       </c>
       <c r="CN18" s="7" t="s">
         <v>1140</v>
       </c>
       <c r="CO18" s="7" t="s">
-        <v>1558</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="19" spans="1:93" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7"/>
       <c r="B19" s="22" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="D19" s="7"/>
       <c r="E19" s="7" t="s">
@@ -52163,7 +52160,7 @@
         <v>845</v>
       </c>
       <c r="BQ19" s="25" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="BS19" s="7" t="s">
         <v>1141</v>
@@ -52185,7 +52182,7 @@
         <v>845</v>
       </c>
       <c r="CI19" s="25" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="CK19" s="7" t="s">
         <v>1141</v>
@@ -52269,7 +52266,7 @@
       <c r="AX20" s="7"/>
       <c r="AY20" s="7"/>
       <c r="AZ20" s="7" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
       <c r="BA20" s="7"/>
       <c r="BB20" s="7"/>
@@ -52287,13 +52284,13 @@
         <v>916</v>
       </c>
       <c r="BQ20" s="25" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="BS20" s="7" t="s">
         <v>1143</v>
       </c>
       <c r="BT20" s="25" t="s">
-        <v>1548</v>
+        <v>1546</v>
       </c>
       <c r="BU20" s="7"/>
       <c r="BV20" s="7"/>
@@ -52309,19 +52306,19 @@
         <v>916</v>
       </c>
       <c r="CI20" s="25" t="s">
-        <v>1555</v>
+        <v>1553</v>
       </c>
       <c r="CK20" s="7" t="s">
         <v>1143</v>
       </c>
       <c r="CL20" s="25" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="CN20" s="7" t="s">
         <v>1143</v>
       </c>
       <c r="CO20" s="25" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="21" spans="1:93" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -52388,7 +52385,7 @@
       <c r="AX21" s="7"/>
       <c r="AY21" s="7"/>
       <c r="AZ21" s="7" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="BA21" s="7"/>
       <c r="BB21" s="7"/>
@@ -52423,7 +52420,7 @@
       <c r="CG21" s="7"/>
       <c r="CH21" s="7"/>
       <c r="CI21" s="7" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="CJ21" s="7"/>
       <c r="CK21" s="7" t="s">
@@ -52700,10 +52697,10 @@
         <v>329</v>
       </c>
       <c r="Y24" s="4" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="Z24" s="4" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="AA24" s="4"/>
       <c r="AB24" s="4"/>
@@ -52752,7 +52749,7 @@
         <v>1151</v>
       </c>
       <c r="BT24" s="35" t="s">
-        <v>1550</v>
+        <v>1548</v>
       </c>
       <c r="BU24" s="7"/>
       <c r="BV24" s="7"/>
@@ -52769,14 +52766,14 @@
       <c r="CK24" s="7" t="s">
         <v>1151</v>
       </c>
-      <c r="CL24" s="45" t="s">
-        <v>1560</v>
+      <c r="CL24" s="25" t="s">
+        <v>1558</v>
       </c>
       <c r="CN24" s="7" t="s">
         <v>1151</v>
       </c>
-      <c r="CO24" s="45" t="s">
-        <v>1560</v>
+      <c r="CO24" s="25" t="s">
+        <v>1558</v>
       </c>
     </row>
     <row r="25" spans="1:93" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -52868,7 +52865,7 @@
         <v>1152</v>
       </c>
       <c r="BT25" s="35" t="s">
-        <v>1551</v>
+        <v>1549</v>
       </c>
       <c r="BU25" s="25"/>
       <c r="BV25" s="25"/>
@@ -52885,15 +52882,15 @@
       <c r="CK25" s="7" t="s">
         <v>1152</v>
       </c>
-      <c r="CL25" s="45" t="s">
-        <v>1556</v>
+      <c r="CL25" s="25" t="s">
+        <v>1554</v>
       </c>
       <c r="CM25" s="7"/>
       <c r="CN25" s="7" t="s">
         <v>1152</v>
       </c>
-      <c r="CO25" s="45" t="s">
-        <v>1556</v>
+      <c r="CO25" s="25" t="s">
+        <v>1554</v>
       </c>
     </row>
     <row r="26" spans="1:93" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -52983,7 +52980,7 @@
         <v>1160</v>
       </c>
       <c r="BT26" s="35" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="BU26" s="25"/>
       <c r="BV26" s="25"/>
@@ -53094,7 +53091,7 @@
         <v>1169</v>
       </c>
       <c r="BT27" s="35" t="s">
-        <v>1553</v>
+        <v>1551</v>
       </c>
       <c r="BU27" s="7"/>
       <c r="BV27" s="7"/>
@@ -54567,7 +54564,7 @@
     </row>
     <row r="44" spans="1:93" x14ac:dyDescent="0.25">
       <c r="B44" s="29" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="AZ44" s="7"/>
       <c r="BA44" s="7"/>
@@ -54601,7 +54598,7 @@
     </row>
     <row r="45" spans="1:93" x14ac:dyDescent="0.25">
       <c r="B45" s="1" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="AZ45" s="7"/>
       <c r="BA45" s="7"/>
@@ -54635,7 +54632,7 @@
     </row>
     <row r="46" spans="1:93" x14ac:dyDescent="0.25">
       <c r="B46" s="1" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="BO46" s="7"/>
       <c r="BP46" s="7"/>
@@ -54666,7 +54663,7 @@
     </row>
     <row r="47" spans="1:93" x14ac:dyDescent="0.25">
       <c r="B47" s="1" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="BO47" s="7"/>
       <c r="BP47" s="7"/>
@@ -54697,7 +54694,7 @@
     </row>
     <row r="48" spans="1:93" x14ac:dyDescent="0.25">
       <c r="B48" s="1" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="BO48" s="7"/>
       <c r="BP48" s="7"/>
@@ -54728,7 +54725,7 @@
     </row>
     <row r="49" spans="2:93" x14ac:dyDescent="0.25">
       <c r="B49" s="1" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="BO49" s="7"/>
       <c r="BP49" s="7"/>
@@ -67941,7 +67938,7 @@
     </row>
     <row r="2" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A2" s="38" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>8</v>
@@ -68094,7 +68091,7 @@
         <v>74</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>1475</v>
+        <v>1473</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>8</v>
@@ -68109,7 +68106,7 @@
         <v>900</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="L3" s="1" t="s">
         <v>8</v>
@@ -68169,19 +68166,19 @@
         <v>8</v>
       </c>
       <c r="AK3" s="7" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="AM3" s="7" t="s">
         <v>8</v>
       </c>
       <c r="AN3" s="7" t="s">
-        <v>1410</v>
+        <v>1408</v>
       </c>
       <c r="AP3" s="7" t="s">
         <v>8</v>
       </c>
       <c r="AQ3" s="22" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="AS3" s="7" t="s">
         <v>8</v>
@@ -68193,7 +68190,7 @@
         <v>8</v>
       </c>
       <c r="AW3" s="1" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="4" spans="1:49" ht="105" x14ac:dyDescent="0.25">
@@ -68202,7 +68199,7 @@
         <v>75</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>410</v>
@@ -68214,10 +68211,10 @@
         <v>667</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>1459</v>
+        <v>1457</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="P4" s="1" t="s">
         <v>8</v>
@@ -68246,7 +68243,7 @@
         <v>173</v>
       </c>
       <c r="AB4" s="7" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
       <c r="AC4" s="7"/>
       <c r="AD4" s="7" t="s">
@@ -68265,19 +68262,19 @@
         <v>522</v>
       </c>
       <c r="AK4" s="7" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="AM4" s="7" t="s">
         <v>516</v>
       </c>
       <c r="AN4" s="7" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="AP4" s="7" t="s">
         <v>517</v>
       </c>
       <c r="AQ4" s="7" t="s">
-        <v>1410</v>
+        <v>1408</v>
       </c>
       <c r="AS4" s="7" t="s">
         <v>350</v>
@@ -68289,19 +68286,19 @@
     <row r="5" spans="1:49" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="4"/>
       <c r="B5" s="4" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>1468</v>
+        <v>1466</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>668</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>1459</v>
+        <v>1457</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="T5" s="1" t="s">
         <v>482</v>
@@ -68357,10 +68354,10 @@
     <row r="6" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="4" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>1469</v>
+        <v>1467</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>669</v>
@@ -68394,10 +68391,10 @@
         <v>173</v>
       </c>
       <c r="AE6" s="7" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
       <c r="AG6" s="18" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="AH6" s="18"/>
       <c r="AJ6" s="7" t="s">
@@ -68420,7 +68417,7 @@
     <row r="7" spans="1:49" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="C7" s="4"/>
       <c r="T7" s="1"/>
@@ -68441,7 +68438,7 @@
       </c>
       <c r="AE7" s="7"/>
       <c r="AG7" s="18" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="AH7" s="18"/>
       <c r="AJ7" s="7" t="s">
@@ -68464,7 +68461,7 @@
     </row>
     <row r="8" spans="1:49" x14ac:dyDescent="0.25">
       <c r="B8" s="4" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="C8" s="4"/>
       <c r="U8" s="1"/>
@@ -68481,7 +68478,7 @@
       </c>
       <c r="AE8" s="7"/>
       <c r="AG8" s="18" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="AH8" s="18"/>
       <c r="AJ8" s="7" t="s">
@@ -68517,7 +68514,7 @@
       </c>
       <c r="AE9" s="7"/>
       <c r="AG9" s="18" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="AH9" s="18"/>
       <c r="AN9" s="8"/>
@@ -68551,7 +68548,7 @@
         <v>274</v>
       </c>
       <c r="AG10" s="7" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="AH10" s="7"/>
       <c r="AN10"/>
@@ -68582,7 +68579,7 @@
       </c>
       <c r="AE11" s="7"/>
       <c r="AG11" s="7" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="AH11" s="7"/>
       <c r="AN11"/>
@@ -68602,7 +68599,7 @@
       </c>
       <c r="AE12" s="7"/>
       <c r="AG12" s="7" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="AH12" s="7"/>
       <c r="AN12"/>
@@ -68735,10 +68732,10 @@
       </c>
       <c r="AB19" s="7"/>
       <c r="AD19" s="22" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="AE19" s="22" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="AN19"/>
       <c r="AP19" s="7" t="s">
@@ -69060,41 +69057,41 @@
       <c r="AA44" s="7"/>
       <c r="AB44" s="7"/>
       <c r="AD44" s="1" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="45" spans="26:31" x14ac:dyDescent="0.25">
       <c r="AA45" s="37"/>
       <c r="AB45" s="7"/>
       <c r="AD45" s="1" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="46" spans="26:31" x14ac:dyDescent="0.25">
       <c r="AA46" s="37"/>
       <c r="AB46" s="7"/>
       <c r="AD46" s="1" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="47" spans="26:31" x14ac:dyDescent="0.25">
       <c r="AA47" s="37"/>
       <c r="AB47" s="7"/>
       <c r="AD47" s="1" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="48" spans="26:31" x14ac:dyDescent="0.25">
       <c r="AA48" s="37"/>
       <c r="AB48" s="7"/>
       <c r="AD48" s="1" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="49" spans="27:30" x14ac:dyDescent="0.25">
       <c r="AA49" s="37"/>
       <c r="AD49" s="1" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="50" spans="27:30" x14ac:dyDescent="0.25">
@@ -69559,10 +69556,10 @@
       </c>
       <c r="AK3" s="7"/>
       <c r="AL3" s="7" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
       <c r="AM3" s="7" t="s">
-        <v>1428</v>
+        <v>1426</v>
       </c>
       <c r="AN3" s="18"/>
       <c r="AO3" s="4" t="s">
@@ -69690,7 +69687,7 @@
       </c>
       <c r="AQ4" s="4"/>
       <c r="AR4" s="4" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="AS4" s="4" t="s">
         <v>568</v>
@@ -69790,10 +69787,10 @@
       <c r="AJ5" s="7"/>
       <c r="AK5" s="7"/>
       <c r="AL5" s="7" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
       <c r="AM5" s="25" t="s">
-        <v>1490</v>
+        <v>1488</v>
       </c>
       <c r="AN5" s="18"/>
       <c r="AO5" s="4" t="s">
@@ -69804,7 +69801,7 @@
       </c>
       <c r="AQ5" s="4"/>
       <c r="AR5" s="4" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="AS5" s="4"/>
       <c r="AT5" s="18"/>
@@ -69828,7 +69825,7 @@
         <v>173</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
       <c r="D6" s="7"/>
       <c r="E6" s="7" t="s">
@@ -70099,20 +70096,20 @@
       <c r="AM8" s="7"/>
       <c r="AN8" s="18"/>
       <c r="AO8" s="18" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="AP8" s="18" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="AQ8" s="4"/>
       <c r="AR8" s="7"/>
       <c r="AS8" s="7"/>
       <c r="AT8" s="18"/>
       <c r="AU8" s="18" t="s">
+        <v>1419</v>
+      </c>
+      <c r="AV8" s="18" t="s">
         <v>1421</v>
-      </c>
-      <c r="AV8" s="18" t="s">
-        <v>1423</v>
       </c>
       <c r="AW8" s="7"/>
       <c r="AX8" s="7" t="s">
@@ -70720,7 +70717,7 @@
         <v>475</v>
       </c>
       <c r="AY17" s="25" t="s">
-        <v>1429</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="18" spans="1:51" ht="90" x14ac:dyDescent="0.25">
@@ -70783,16 +70780,16 @@
         <v>476</v>
       </c>
       <c r="AY18" s="25" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="19" spans="1:51" ht="90" x14ac:dyDescent="0.25">
       <c r="A19" s="7"/>
       <c r="B19" s="22" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="D19" s="7"/>
       <c r="E19" s="7" t="s">
@@ -70844,7 +70841,7 @@
         <v>845</v>
       </c>
       <c r="AY19" s="25" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="20" spans="1:51" x14ac:dyDescent="0.25">
@@ -70888,7 +70885,7 @@
       <c r="AG20" s="7"/>
       <c r="AH20" s="7"/>
       <c r="AI20" s="7" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
       <c r="AJ20" s="7"/>
       <c r="AK20" s="7"/>
@@ -70948,7 +70945,7 @@
       <c r="AG21" s="7"/>
       <c r="AH21" s="7"/>
       <c r="AI21" s="7" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="AJ21" s="7"/>
       <c r="AK21" s="7"/>
@@ -71113,7 +71110,7 @@
         <v>329</v>
       </c>
       <c r="U24" s="4" t="s">
-        <v>1489</v>
+        <v>1487</v>
       </c>
       <c r="Y24" s="7"/>
       <c r="Z24" s="7"/>
@@ -72121,36 +72118,36 @@
     </row>
     <row r="44" spans="1:51" x14ac:dyDescent="0.25">
       <c r="B44" s="1" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="AI44" s="7"/>
       <c r="AJ44" s="7"/>
     </row>
     <row r="45" spans="1:51" x14ac:dyDescent="0.25">
       <c r="B45" s="1" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="AI45" s="7"/>
       <c r="AJ45" s="7"/>
     </row>
     <row r="46" spans="1:51" x14ac:dyDescent="0.25">
       <c r="B46" s="1" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="47" spans="1:51" x14ac:dyDescent="0.25">
       <c r="B47" s="1" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="48" spans="1:51" x14ac:dyDescent="0.25">
       <c r="B48" s="1" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="49" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B49" s="1" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
     </row>
   </sheetData>
@@ -72564,7 +72561,7 @@
       </c>
       <c r="AJ3" s="7"/>
       <c r="AK3" s="7" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
       <c r="AL3" s="7" t="s">
         <v>815</v>
@@ -72692,7 +72689,7 @@
       </c>
       <c r="AP4" s="4"/>
       <c r="AQ4" s="4" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="AR4" s="4" t="s">
         <v>568</v>
@@ -72789,10 +72786,10 @@
       <c r="AI5" s="7"/>
       <c r="AJ5" s="7"/>
       <c r="AK5" s="26" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
       <c r="AL5" s="25" t="s">
-        <v>1490</v>
+        <v>1488</v>
       </c>
       <c r="AM5" s="18"/>
       <c r="AN5" s="4" t="s">
@@ -72803,7 +72800,7 @@
       </c>
       <c r="AP5" s="4"/>
       <c r="AQ5" s="4" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="AR5" s="4"/>
       <c r="AS5" s="18"/>
@@ -72827,7 +72824,7 @@
         <v>173</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
       <c r="D6" s="7"/>
       <c r="E6" s="7" t="s">
@@ -73091,20 +73088,20 @@
       <c r="AL8" s="7"/>
       <c r="AM8" s="18"/>
       <c r="AN8" s="18" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="AO8" s="18" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="AP8" s="4"/>
       <c r="AQ8" s="7"/>
       <c r="AR8" s="7"/>
       <c r="AS8" s="18"/>
       <c r="AT8" s="18" t="s">
+        <v>1419</v>
+      </c>
+      <c r="AU8" s="18" t="s">
         <v>1421</v>
-      </c>
-      <c r="AU8" s="18" t="s">
-        <v>1423</v>
       </c>
       <c r="AV8" s="7"/>
       <c r="AW8" s="7" t="s">
@@ -73354,7 +73351,7 @@
         <v>252</v>
       </c>
       <c r="F12" s="26" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="G12" s="4"/>
       <c r="H12" s="4" t="s">
@@ -73657,7 +73654,7 @@
         <v>257</v>
       </c>
       <c r="F17" s="26" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="G17" s="7"/>
       <c r="H17" s="7"/>
@@ -73701,7 +73698,7 @@
         <v>475</v>
       </c>
       <c r="AX17" s="25" t="s">
-        <v>1426</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="18" spans="1:50" ht="75" x14ac:dyDescent="0.25">
@@ -73763,16 +73760,16 @@
         <v>476</v>
       </c>
       <c r="AX18" s="25" t="s">
-        <v>1427</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="19" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A19" s="7"/>
       <c r="B19" s="22" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="D19" s="7"/>
       <c r="E19" s="7" t="s">
@@ -73862,7 +73859,7 @@
       <c r="AF20" s="7"/>
       <c r="AG20" s="7"/>
       <c r="AH20" s="7" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
       <c r="AI20" s="7"/>
       <c r="AJ20" s="7"/>
@@ -73921,7 +73918,7 @@
       <c r="AF21" s="7"/>
       <c r="AG21" s="7"/>
       <c r="AH21" s="7" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="AI21" s="7"/>
       <c r="AJ21" s="7"/>
@@ -74083,7 +74080,7 @@
         <v>329</v>
       </c>
       <c r="T24" s="4" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="X24" s="7"/>
       <c r="Y24" s="7"/>
@@ -75075,7 +75072,7 @@
     </row>
     <row r="44" spans="1:50" x14ac:dyDescent="0.25">
       <c r="B44" s="29" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="C44" s="29"/>
       <c r="AH44" s="7"/>
@@ -75083,29 +75080,29 @@
     </row>
     <row r="45" spans="1:50" x14ac:dyDescent="0.25">
       <c r="B45" s="1" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="AH45" s="7"/>
       <c r="AI45" s="7"/>
     </row>
     <row r="46" spans="1:50" x14ac:dyDescent="0.25">
       <c r="B46" s="1" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="47" spans="1:50" x14ac:dyDescent="0.25">
       <c r="B47" s="1" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="48" spans="1:50" x14ac:dyDescent="0.25">
       <c r="B48" s="1" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="49" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B49" s="1" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
     </row>
   </sheetData>
@@ -75617,7 +75614,7 @@
       </c>
       <c r="AV3" s="7"/>
       <c r="AW3" s="7" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
       <c r="AX3" s="7" t="s">
         <v>811</v>
@@ -75779,7 +75776,7 @@
       </c>
       <c r="BB4" s="4"/>
       <c r="BC4" s="4" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="BD4" s="4" t="s">
         <v>568</v>
@@ -75905,10 +75902,10 @@
       <c r="AU5" s="7"/>
       <c r="AV5" s="7"/>
       <c r="AW5" s="26" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
       <c r="AX5" s="25" t="s">
-        <v>1490</v>
+        <v>1488</v>
       </c>
       <c r="AY5" s="18"/>
       <c r="AZ5" s="4" t="s">
@@ -75919,7 +75916,7 @@
       </c>
       <c r="BB5" s="4"/>
       <c r="BC5" s="4" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="BD5" s="4"/>
       <c r="BE5" s="18"/>
@@ -75943,7 +75940,7 @@
         <v>173</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
       <c r="D6" s="7"/>
       <c r="E6" s="7" t="s">
@@ -76004,7 +76001,7 @@
       <c r="AH6" s="7"/>
       <c r="AI6" s="7"/>
       <c r="AJ6" s="7" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="AK6" s="7"/>
       <c r="AL6" s="7"/>
@@ -76134,7 +76131,7 @@
       <c r="AH7" s="7"/>
       <c r="AI7" s="7"/>
       <c r="AJ7" s="7" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="AK7" s="7"/>
       <c r="AL7" s="7"/>
@@ -76256,7 +76253,7 @@
       <c r="AH8" s="7"/>
       <c r="AI8" s="7"/>
       <c r="AJ8" s="7" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="AK8" s="7"/>
       <c r="AL8" s="7"/>
@@ -76286,20 +76283,20 @@
       <c r="AX8" s="7"/>
       <c r="AY8" s="18"/>
       <c r="AZ8" s="18" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="BA8" s="18" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="BB8" s="4"/>
       <c r="BC8" s="7"/>
       <c r="BD8" s="7"/>
       <c r="BE8" s="18"/>
       <c r="BF8" s="18" t="s">
+        <v>1419</v>
+      </c>
+      <c r="BG8" s="18" t="s">
         <v>1421</v>
-      </c>
-      <c r="BG8" s="18" t="s">
-        <v>1423</v>
       </c>
       <c r="BH8" s="7"/>
       <c r="BI8" s="7" t="s">
@@ -76368,7 +76365,7 @@
       <c r="AH9" s="7"/>
       <c r="AI9" s="7"/>
       <c r="AJ9" s="7" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="AK9" s="7"/>
       <c r="AL9" s="7"/>
@@ -76478,7 +76475,7 @@
       <c r="AH10" s="7"/>
       <c r="AI10" s="7"/>
       <c r="AJ10" s="7" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="AK10" s="7"/>
       <c r="AL10" s="7"/>
@@ -76576,7 +76573,7 @@
       <c r="AH11" s="7"/>
       <c r="AI11" s="7"/>
       <c r="AJ11" s="7" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="AK11" s="7"/>
       <c r="AL11" s="7"/>
@@ -76624,7 +76621,7 @@
         <v>252</v>
       </c>
       <c r="F12" s="26" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="G12" s="4"/>
       <c r="H12" s="4" t="s">
@@ -77046,7 +77043,7 @@
         <v>257</v>
       </c>
       <c r="F17" s="26" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="G17" s="7"/>
       <c r="H17" s="7"/>
@@ -77116,7 +77113,7 @@
         <v>475</v>
       </c>
       <c r="BJ17" s="25" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="18" spans="1:62" ht="45" x14ac:dyDescent="0.25">
@@ -77200,7 +77197,7 @@
         <v>476</v>
       </c>
       <c r="BJ18" s="25" t="s">
-        <v>1433</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="19" spans="1:62" ht="45" x14ac:dyDescent="0.25">
@@ -77284,7 +77281,7 @@
         <v>845</v>
       </c>
       <c r="BJ19" s="25" t="s">
-        <v>1434</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="20" spans="1:62" x14ac:dyDescent="0.25">
@@ -77636,7 +77633,7 @@
         <v>329</v>
       </c>
       <c r="V24" s="4" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="W24" s="4"/>
       <c r="X24" s="4"/>
@@ -78546,7 +78543,7 @@
       <c r="AR36" s="7"/>
       <c r="AS36" s="7"/>
       <c r="AT36" s="7" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
       <c r="AU36" s="7"/>
       <c r="AV36" s="7"/>
@@ -78620,7 +78617,7 @@
       <c r="AR37" s="7"/>
       <c r="AS37" s="7"/>
       <c r="AT37" s="7" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="AU37" s="7"/>
       <c r="AV37" s="7"/>
@@ -78989,40 +78986,40 @@
     </row>
     <row r="43" spans="1:62" x14ac:dyDescent="0.25">
       <c r="B43" s="1" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="44" spans="1:62" x14ac:dyDescent="0.25">
       <c r="B44" s="1" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="45" spans="1:62" x14ac:dyDescent="0.25">
       <c r="B45" s="1" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="46" spans="1:62" x14ac:dyDescent="0.25">
       <c r="B46" s="1" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="47" spans="1:62" x14ac:dyDescent="0.25">
       <c r="B47" s="1" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="48" spans="1:62" x14ac:dyDescent="0.25">
       <c r="B48" s="1" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="49" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B49" s="1" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
     </row>
   </sheetData>
@@ -79586,7 +79583,7 @@
       </c>
       <c r="BB3" s="7"/>
       <c r="BC3" s="7" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
       <c r="BD3" s="7" t="s">
         <v>1053</v>
@@ -79762,7 +79759,7 @@
       </c>
       <c r="BH4" s="4"/>
       <c r="BI4" s="4" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="BJ4" s="4" t="s">
         <v>568</v>
@@ -79902,10 +79899,10 @@
       <c r="BA5" s="7"/>
       <c r="BB5" s="7"/>
       <c r="BC5" s="26" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
       <c r="BD5" s="25" t="s">
-        <v>1490</v>
+        <v>1488</v>
       </c>
       <c r="BE5" s="18"/>
       <c r="BF5" s="4" t="s">
@@ -79916,7 +79913,7 @@
       </c>
       <c r="BH5" s="4"/>
       <c r="BI5" s="4" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="BJ5" s="4"/>
       <c r="BK5" s="18"/>
@@ -79940,7 +79937,7 @@
         <v>173</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
       <c r="D6" s="7"/>
       <c r="E6" s="7" t="s">
@@ -80008,7 +80005,7 @@
       <c r="AM6" s="7"/>
       <c r="AN6" s="7"/>
       <c r="AO6" s="7" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="AP6" s="7"/>
       <c r="AQ6" s="7"/>
@@ -80154,7 +80151,7 @@
       <c r="AM7" s="7"/>
       <c r="AN7" s="7"/>
       <c r="AO7" s="7" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="AP7" s="7"/>
       <c r="AQ7" s="7"/>
@@ -80286,7 +80283,7 @@
       <c r="AM8" s="7"/>
       <c r="AN8" s="7"/>
       <c r="AO8" s="7" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="AP8" s="7"/>
       <c r="AQ8" s="7"/>
@@ -80317,20 +80314,20 @@
       <c r="BD8" s="7"/>
       <c r="BE8" s="18"/>
       <c r="BF8" s="18" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="BG8" s="18" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="BH8" s="4"/>
       <c r="BI8" s="7"/>
       <c r="BJ8" s="7"/>
       <c r="BK8" s="18"/>
       <c r="BL8" s="18" t="s">
+        <v>1419</v>
+      </c>
+      <c r="BM8" s="18" t="s">
         <v>1421</v>
-      </c>
-      <c r="BM8" s="18" t="s">
-        <v>1423</v>
       </c>
       <c r="BN8" s="7"/>
       <c r="BO8" s="7" t="s">
@@ -80408,7 +80405,7 @@
       <c r="AM9" s="7"/>
       <c r="AN9" s="7"/>
       <c r="AO9" s="7" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="AP9" s="7"/>
       <c r="AQ9" s="7"/>
@@ -80524,7 +80521,7 @@
       <c r="AM10" s="7"/>
       <c r="AN10" s="7"/>
       <c r="AO10" s="7" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="AP10" s="7"/>
       <c r="AQ10" s="7"/>
@@ -80630,7 +80627,7 @@
       <c r="AM11" s="7"/>
       <c r="AN11" s="7"/>
       <c r="AO11" s="7" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="AP11" s="7"/>
       <c r="AQ11" s="7"/>
@@ -80681,7 +80678,7 @@
         <v>252</v>
       </c>
       <c r="F12" s="26" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="G12" s="4"/>
       <c r="H12" s="4" t="s">
@@ -81143,7 +81140,7 @@
         <v>257</v>
       </c>
       <c r="F17" s="26" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="G17" s="7"/>
       <c r="H17" s="7"/>
@@ -81219,7 +81216,7 @@
         <v>475</v>
       </c>
       <c r="BP17" s="25" t="s">
-        <v>1435</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="18" spans="1:68" ht="105" x14ac:dyDescent="0.25">
@@ -81311,7 +81308,7 @@
         <v>476</v>
       </c>
       <c r="BP18" s="25" t="s">
-        <v>1436</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="19" spans="1:68" ht="30" x14ac:dyDescent="0.25">
@@ -81787,10 +81784,10 @@
         <v>329</v>
       </c>
       <c r="T24" s="4" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="U24" s="4" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="V24" s="4"/>
       <c r="W24" s="4"/>
@@ -82788,7 +82785,7 @@
       <c r="AW36" s="7"/>
       <c r="AX36" s="7"/>
       <c r="AY36" s="7" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
       <c r="AZ36" s="7"/>
       <c r="BA36" s="7"/>
@@ -82868,7 +82865,7 @@
       <c r="AW37" s="7"/>
       <c r="AX37" s="7"/>
       <c r="AY37" s="7" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="AZ37" s="7"/>
       <c r="BA37" s="7"/>
@@ -83256,40 +83253,40 @@
     </row>
     <row r="43" spans="1:68" x14ac:dyDescent="0.25">
       <c r="B43" s="1" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="44" spans="1:68" x14ac:dyDescent="0.25">
       <c r="B44" s="1" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="45" spans="1:68" x14ac:dyDescent="0.25">
       <c r="B45" s="1" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="46" spans="1:68" x14ac:dyDescent="0.25">
       <c r="B46" s="1" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="47" spans="1:68" x14ac:dyDescent="0.25">
       <c r="B47" s="1" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="48" spans="1:68" x14ac:dyDescent="0.25">
       <c r="B48" s="1" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="49" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B49" s="1" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
     </row>
   </sheetData>
@@ -83886,7 +83883,7 @@
       </c>
       <c r="BE3" s="7"/>
       <c r="BF3" s="7" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
       <c r="BG3" s="7" t="s">
         <v>809</v>
@@ -84074,7 +84071,7 @@
       </c>
       <c r="BK4" s="4"/>
       <c r="BL4" s="4" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="BM4" s="4" t="s">
         <v>568</v>
@@ -84226,10 +84223,10 @@
       <c r="BD5" s="7"/>
       <c r="BE5" s="7"/>
       <c r="BF5" s="26" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
       <c r="BG5" s="25" t="s">
-        <v>1490</v>
+        <v>1488</v>
       </c>
       <c r="BH5" s="18"/>
       <c r="BI5" s="4" t="s">
@@ -84240,7 +84237,7 @@
       </c>
       <c r="BK5" s="4"/>
       <c r="BL5" s="4" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="BM5" s="4"/>
       <c r="BN5" s="18"/>
@@ -84267,7 +84264,7 @@
         <v>173</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
       <c r="D6" s="7"/>
       <c r="E6" s="7" t="s">
@@ -84344,7 +84341,7 @@
       <c r="AP6" s="7"/>
       <c r="AQ6" s="7"/>
       <c r="AR6" s="7" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="AS6" s="7"/>
       <c r="AT6" s="7"/>
@@ -84496,7 +84493,7 @@
       <c r="AP7" s="7"/>
       <c r="AQ7" s="7"/>
       <c r="AR7" s="7" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="AS7" s="7"/>
       <c r="AT7" s="7"/>
@@ -84634,7 +84631,7 @@
       <c r="AP8" s="7"/>
       <c r="AQ8" s="7"/>
       <c r="AR8" s="7" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="AS8" s="7"/>
       <c r="AT8" s="7"/>
@@ -84665,20 +84662,20 @@
       <c r="BG8" s="7"/>
       <c r="BH8" s="18"/>
       <c r="BI8" s="18" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="BJ8" s="18" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="BK8" s="4"/>
       <c r="BL8" s="7"/>
       <c r="BM8" s="7"/>
       <c r="BN8" s="18"/>
       <c r="BO8" s="18" t="s">
+        <v>1419</v>
+      </c>
+      <c r="BP8" s="18" t="s">
         <v>1421</v>
-      </c>
-      <c r="BP8" s="18" t="s">
-        <v>1423</v>
       </c>
       <c r="BQ8" s="7"/>
       <c r="BR8" s="7" t="s">
@@ -84760,7 +84757,7 @@
       <c r="AP9" s="7"/>
       <c r="AQ9" s="7"/>
       <c r="AR9" s="7" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="AS9" s="7"/>
       <c r="AT9" s="7"/>
@@ -84884,7 +84881,7 @@
       <c r="AP10" s="7"/>
       <c r="AQ10" s="7"/>
       <c r="AR10" s="7" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="AS10" s="7"/>
       <c r="AT10" s="7"/>
@@ -84996,7 +84993,7 @@
       <c r="AP11" s="7"/>
       <c r="AQ11" s="7"/>
       <c r="AR11" s="7" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="AS11" s="7"/>
       <c r="AT11" s="7"/>
@@ -85048,10 +85045,10 @@
         <v>252</v>
       </c>
       <c r="F12" s="26" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="G12" s="26" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="H12" s="4"/>
       <c r="I12" s="4" t="s">
@@ -85542,10 +85539,10 @@
         <v>257</v>
       </c>
       <c r="F17" s="26" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="G17" s="26" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="H17" s="7"/>
       <c r="I17" s="7"/>
@@ -85623,10 +85620,10 @@
         <v>475</v>
       </c>
       <c r="BS17" s="25" t="s">
+        <v>1435</v>
+      </c>
+      <c r="BT17" s="25" t="s">
         <v>1437</v>
-      </c>
-      <c r="BT17" s="25" t="s">
-        <v>1439</v>
       </c>
     </row>
     <row r="18" spans="1:72" ht="90" x14ac:dyDescent="0.25">
@@ -85723,10 +85720,10 @@
         <v>476</v>
       </c>
       <c r="BS18" s="25" t="s">
+        <v>1436</v>
+      </c>
+      <c r="BT18" s="25" t="s">
         <v>1438</v>
-      </c>
-      <c r="BT18" s="25" t="s">
-        <v>1440</v>
       </c>
     </row>
     <row r="19" spans="1:72" x14ac:dyDescent="0.25">
@@ -86237,10 +86234,10 @@
         <v>329</v>
       </c>
       <c r="W24" s="4" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="X24" s="4" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="Y24" s="4"/>
       <c r="Z24" s="4"/>
@@ -87302,7 +87299,7 @@
       <c r="AZ36" s="7"/>
       <c r="BA36" s="7"/>
       <c r="BB36" s="7" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
       <c r="BC36" s="7"/>
       <c r="BD36" s="7"/>
@@ -87388,7 +87385,7 @@
       <c r="AZ37" s="7"/>
       <c r="BA37" s="7"/>
       <c r="BB37" s="7" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="BC37" s="7"/>
       <c r="BD37" s="7"/>
@@ -87815,40 +87812,40 @@
     </row>
     <row r="43" spans="1:72" x14ac:dyDescent="0.25">
       <c r="B43" s="1" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="44" spans="1:72" x14ac:dyDescent="0.25">
       <c r="B44" s="1" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="45" spans="1:72" x14ac:dyDescent="0.25">
       <c r="B45" s="1" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="46" spans="1:72" x14ac:dyDescent="0.25">
       <c r="B46" s="1" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="47" spans="1:72" x14ac:dyDescent="0.25">
       <c r="B47" s="1" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="48" spans="1:72" x14ac:dyDescent="0.25">
       <c r="B48" s="1" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="49" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B49" s="1" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
     </row>
   </sheetData>
